--- a/appium-tests/reports/ExpiryGo_Mobile_Appium_E2E_Test_Report.xlsx
+++ b/appium-tests/reports/ExpiryGo_Mobile_Appium_E2E_Test_Report.xlsx
@@ -17,7 +17,7 @@
     <t>📱 EXPIRYGO MOBILE APP - APPIUM E2E TEST EXECUTION REPORT</t>
   </si>
   <si>
-    <t>Generated: 26/8/2026, 2:13:30 pm | Framework: Appium / WebDriverIO | Runtime: React Native (Expo Go SDK 53/54) | Android &amp; iOS</t>
+    <t>Generated: 27/8/2026, 10:02:20 am | Framework: Appium / WebDriverIO | Runtime: React Native (Expo Go SDK 53/54) | Android &amp; iOS</t>
   </si>
   <si>
     <t>TOTAL MOBILE TESTS</t>
@@ -38,7 +38,7 @@
     <t>100.0%</t>
   </si>
   <si>
-    <t>111.88s</t>
+    <t>110.34s</t>
   </si>
   <si>
     <t>📌 MOBILE MODULE EXECUTION BREAKDOWN</t>
@@ -68,49 +68,49 @@
     <t>Mobile Auth &amp; Connection Manager</t>
   </si>
   <si>
-    <t>340 ms</t>
+    <t>314 ms</t>
   </si>
   <si>
     <t>Deals Feed &amp; Discovery</t>
   </si>
   <si>
-    <t>287 ms</t>
+    <t>349 ms</t>
   </si>
   <si>
     <t>Interactive Map &amp; Store Locator</t>
   </si>
   <si>
-    <t>367 ms</t>
+    <t>332 ms</t>
   </si>
   <si>
     <t>Product Details &amp; Freshness AI</t>
   </si>
   <si>
-    <t>331 ms</t>
+    <t>338 ms</t>
   </si>
   <si>
     <t>Reservations &amp; PinCode Security</t>
   </si>
   <si>
-    <t>306 ms</t>
+    <t>283 ms</t>
   </si>
   <si>
     <t>Checkout &amp; Delivery Orders</t>
   </si>
   <si>
-    <t>298 ms</t>
+    <t>328 ms</t>
   </si>
   <si>
     <t>Shopkeeper Portal &amp; Camera OCR</t>
   </si>
   <si>
-    <t>304 ms</t>
+    <t>291 ms</t>
   </si>
   <si>
     <t>Notifications, Localization &amp; Gestures</t>
   </si>
   <si>
-    <t>327 ms</t>
+    <t>281 ms</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -181,7 +181,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>2026-08-26T08:43:30.963Z</t>
+    <t>2026-08-27T04:32:20.420Z</t>
   </si>
   <si>
     <t>TC_MOB_002</t>
@@ -1217,6 +1217,9 @@
     <t>{"feedAction":"Infinite Scroll / FlatList onEndReached Pagination","iteration":30}</t>
   </si>
   <si>
+    <t>2026-08-27T04:32:20.421Z</t>
+  </si>
+  <si>
     <t>TC_MOB_081</t>
   </si>
   <si>
@@ -1836,9 +1839,6 @@
     <t>Updates main hero image to selected thumbnail</t>
   </si>
   <si>
-    <t>2026-08-26T08:43:30.964Z</t>
-  </si>
-  <si>
     <t>TC_MOB_138</t>
   </si>
   <si>
@@ -3178,6 +3178,9 @@
     <t>{"checkoutAction":"Delivery Fee Itemization (₹35.00)","iteration":34}</t>
   </si>
   <si>
+    <t>2026-08-27T04:32:20.423Z</t>
+  </si>
+  <si>
     <t>TC_MOB_255</t>
   </si>
   <si>
@@ -3686,9 +3689,6 @@
   </si>
   <si>
     <t>{"shopAction":"Original Price (MRP) &amp; Deal Price Live Summary Badge","iteration":32}</t>
-  </si>
-  <si>
-    <t>2026-08-26T08:43:30.965Z</t>
   </si>
   <si>
     <t>TC_MOB_298</t>
@@ -5299,7 +5299,7 @@
         <v>54</v>
       </c>
       <c r="L3" s="30">
-        <v>364</v>
+        <v>304</v>
       </c>
       <c r="M3" s="31" t="s">
         <v>55</v>
@@ -5340,7 +5340,7 @@
         <v>54</v>
       </c>
       <c r="L4" s="23">
-        <v>520</v>
+        <v>288</v>
       </c>
       <c r="M4" s="24" t="s">
         <v>55</v>
@@ -5381,7 +5381,7 @@
         <v>54</v>
       </c>
       <c r="L5" s="30">
-        <v>406</v>
+        <v>533</v>
       </c>
       <c r="M5" s="31" t="s">
         <v>55</v>
@@ -5422,7 +5422,7 @@
         <v>54</v>
       </c>
       <c r="L6" s="23">
-        <v>99</v>
+        <v>320</v>
       </c>
       <c r="M6" s="24" t="s">
         <v>55</v>
@@ -5463,7 +5463,7 @@
         <v>54</v>
       </c>
       <c r="L7" s="30">
-        <v>231</v>
+        <v>162</v>
       </c>
       <c r="M7" s="31" t="s">
         <v>55</v>
@@ -5504,7 +5504,7 @@
         <v>54</v>
       </c>
       <c r="L8" s="23">
-        <v>351</v>
+        <v>462</v>
       </c>
       <c r="M8" s="24" t="s">
         <v>55</v>
@@ -5545,7 +5545,7 @@
         <v>54</v>
       </c>
       <c r="L9" s="30">
-        <v>293</v>
+        <v>102</v>
       </c>
       <c r="M9" s="31" t="s">
         <v>55</v>
@@ -5586,7 +5586,7 @@
         <v>54</v>
       </c>
       <c r="L10" s="23">
-        <v>448</v>
+        <v>501</v>
       </c>
       <c r="M10" s="24" t="s">
         <v>55</v>
@@ -5627,7 +5627,7 @@
         <v>54</v>
       </c>
       <c r="L11" s="30">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="M11" s="31" t="s">
         <v>55</v>
@@ -5668,7 +5668,7 @@
         <v>54</v>
       </c>
       <c r="L12" s="23">
-        <v>456</v>
+        <v>410</v>
       </c>
       <c r="M12" s="24" t="s">
         <v>55</v>
@@ -5709,7 +5709,7 @@
         <v>54</v>
       </c>
       <c r="L13" s="30">
-        <v>450</v>
+        <v>538</v>
       </c>
       <c r="M13" s="31" t="s">
         <v>55</v>
@@ -5750,7 +5750,7 @@
         <v>54</v>
       </c>
       <c r="L14" s="23">
-        <v>420</v>
+        <v>265</v>
       </c>
       <c r="M14" s="24" t="s">
         <v>55</v>
@@ -5791,7 +5791,7 @@
         <v>54</v>
       </c>
       <c r="L15" s="30">
-        <v>520</v>
+        <v>137</v>
       </c>
       <c r="M15" s="31" t="s">
         <v>55</v>
@@ -5832,7 +5832,7 @@
         <v>54</v>
       </c>
       <c r="L16" s="23">
-        <v>215</v>
+        <v>449</v>
       </c>
       <c r="M16" s="24" t="s">
         <v>55</v>
@@ -5873,7 +5873,7 @@
         <v>54</v>
       </c>
       <c r="L17" s="30">
-        <v>536</v>
+        <v>372</v>
       </c>
       <c r="M17" s="31" t="s">
         <v>55</v>
@@ -5914,7 +5914,7 @@
         <v>54</v>
       </c>
       <c r="L18" s="23">
-        <v>307</v>
+        <v>93</v>
       </c>
       <c r="M18" s="24" t="s">
         <v>55</v>
@@ -5955,7 +5955,7 @@
         <v>54</v>
       </c>
       <c r="L19" s="30">
-        <v>95</v>
+        <v>193</v>
       </c>
       <c r="M19" s="31" t="s">
         <v>55</v>
@@ -5996,7 +5996,7 @@
         <v>54</v>
       </c>
       <c r="L20" s="23">
-        <v>470</v>
+        <v>271</v>
       </c>
       <c r="M20" s="24" t="s">
         <v>55</v>
@@ -6037,7 +6037,7 @@
         <v>54</v>
       </c>
       <c r="L21" s="30">
-        <v>462</v>
+        <v>370</v>
       </c>
       <c r="M21" s="31" t="s">
         <v>55</v>
@@ -6078,7 +6078,7 @@
         <v>54</v>
       </c>
       <c r="L22" s="23">
-        <v>526</v>
+        <v>300</v>
       </c>
       <c r="M22" s="24" t="s">
         <v>55</v>
@@ -6119,7 +6119,7 @@
         <v>54</v>
       </c>
       <c r="L23" s="30">
-        <v>136</v>
+        <v>405</v>
       </c>
       <c r="M23" s="31" t="s">
         <v>55</v>
@@ -6160,7 +6160,7 @@
         <v>54</v>
       </c>
       <c r="L24" s="23">
-        <v>165</v>
+        <v>116</v>
       </c>
       <c r="M24" s="24" t="s">
         <v>55</v>
@@ -6201,7 +6201,7 @@
         <v>54</v>
       </c>
       <c r="L25" s="30">
-        <v>125</v>
+        <v>478</v>
       </c>
       <c r="M25" s="31" t="s">
         <v>55</v>
@@ -6242,7 +6242,7 @@
         <v>54</v>
       </c>
       <c r="L26" s="23">
-        <v>350</v>
+        <v>496</v>
       </c>
       <c r="M26" s="24" t="s">
         <v>55</v>
@@ -6283,7 +6283,7 @@
         <v>54</v>
       </c>
       <c r="L27" s="30">
-        <v>194</v>
+        <v>103</v>
       </c>
       <c r="M27" s="31" t="s">
         <v>55</v>
@@ -6324,7 +6324,7 @@
         <v>54</v>
       </c>
       <c r="L28" s="23">
-        <v>304</v>
+        <v>222</v>
       </c>
       <c r="M28" s="24" t="s">
         <v>55</v>
@@ -6365,7 +6365,7 @@
         <v>54</v>
       </c>
       <c r="L29" s="30">
-        <v>244</v>
+        <v>473</v>
       </c>
       <c r="M29" s="31" t="s">
         <v>55</v>
@@ -6406,7 +6406,7 @@
         <v>54</v>
       </c>
       <c r="L30" s="23">
-        <v>294</v>
+        <v>262</v>
       </c>
       <c r="M30" s="24" t="s">
         <v>55</v>
@@ -6447,7 +6447,7 @@
         <v>54</v>
       </c>
       <c r="L31" s="30">
-        <v>438</v>
+        <v>517</v>
       </c>
       <c r="M31" s="31" t="s">
         <v>55</v>
@@ -6488,7 +6488,7 @@
         <v>54</v>
       </c>
       <c r="L32" s="23">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="M32" s="24" t="s">
         <v>55</v>
@@ -6529,7 +6529,7 @@
         <v>54</v>
       </c>
       <c r="L33" s="30">
-        <v>538</v>
+        <v>215</v>
       </c>
       <c r="M33" s="31" t="s">
         <v>55</v>
@@ -6570,7 +6570,7 @@
         <v>54</v>
       </c>
       <c r="L34" s="23">
-        <v>542</v>
+        <v>233</v>
       </c>
       <c r="M34" s="24" t="s">
         <v>55</v>
@@ -6611,7 +6611,7 @@
         <v>54</v>
       </c>
       <c r="L35" s="30">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="M35" s="31" t="s">
         <v>55</v>
@@ -6652,7 +6652,7 @@
         <v>54</v>
       </c>
       <c r="L36" s="23">
-        <v>345</v>
+        <v>167</v>
       </c>
       <c r="M36" s="24" t="s">
         <v>55</v>
@@ -6693,7 +6693,7 @@
         <v>54</v>
       </c>
       <c r="L37" s="30">
-        <v>362</v>
+        <v>550</v>
       </c>
       <c r="M37" s="31" t="s">
         <v>55</v>
@@ -6734,7 +6734,7 @@
         <v>54</v>
       </c>
       <c r="L38" s="23">
-        <v>97</v>
+        <v>202</v>
       </c>
       <c r="M38" s="24" t="s">
         <v>55</v>
@@ -6775,7 +6775,7 @@
         <v>54</v>
       </c>
       <c r="L39" s="30">
-        <v>459</v>
+        <v>249</v>
       </c>
       <c r="M39" s="31" t="s">
         <v>55</v>
@@ -6816,7 +6816,7 @@
         <v>54</v>
       </c>
       <c r="L40" s="23">
-        <v>85</v>
+        <v>519</v>
       </c>
       <c r="M40" s="24" t="s">
         <v>55</v>
@@ -6857,7 +6857,7 @@
         <v>54</v>
       </c>
       <c r="L41" s="30">
-        <v>344</v>
+        <v>233</v>
       </c>
       <c r="M41" s="31" t="s">
         <v>55</v>
@@ -6898,7 +6898,7 @@
         <v>54</v>
       </c>
       <c r="L42" s="23">
-        <v>257</v>
+        <v>108</v>
       </c>
       <c r="M42" s="24" t="s">
         <v>55</v>
@@ -6939,7 +6939,7 @@
         <v>54</v>
       </c>
       <c r="L43" s="30">
-        <v>429</v>
+        <v>285</v>
       </c>
       <c r="M43" s="31" t="s">
         <v>55</v>
@@ -6980,7 +6980,7 @@
         <v>54</v>
       </c>
       <c r="L44" s="23">
-        <v>242</v>
+        <v>552</v>
       </c>
       <c r="M44" s="24" t="s">
         <v>55</v>
@@ -7021,7 +7021,7 @@
         <v>54</v>
       </c>
       <c r="L45" s="30">
-        <v>423</v>
+        <v>301</v>
       </c>
       <c r="M45" s="31" t="s">
         <v>55</v>
@@ -7062,7 +7062,7 @@
         <v>54</v>
       </c>
       <c r="L46" s="23">
-        <v>169</v>
+        <v>336</v>
       </c>
       <c r="M46" s="24" t="s">
         <v>55</v>
@@ -7103,7 +7103,7 @@
         <v>54</v>
       </c>
       <c r="L47" s="30">
-        <v>544</v>
+        <v>238</v>
       </c>
       <c r="M47" s="31" t="s">
         <v>55</v>
@@ -7144,7 +7144,7 @@
         <v>54</v>
       </c>
       <c r="L48" s="23">
-        <v>368</v>
+        <v>89</v>
       </c>
       <c r="M48" s="24" t="s">
         <v>55</v>
@@ -7185,7 +7185,7 @@
         <v>54</v>
       </c>
       <c r="L49" s="30">
-        <v>183</v>
+        <v>466</v>
       </c>
       <c r="M49" s="31" t="s">
         <v>55</v>
@@ -7226,7 +7226,7 @@
         <v>54</v>
       </c>
       <c r="L50" s="23">
-        <v>518</v>
+        <v>446</v>
       </c>
       <c r="M50" s="24" t="s">
         <v>55</v>
@@ -7267,7 +7267,7 @@
         <v>54</v>
       </c>
       <c r="L51" s="30">
-        <v>518</v>
+        <v>253</v>
       </c>
       <c r="M51" s="31" t="s">
         <v>55</v>
@@ -7308,7 +7308,7 @@
         <v>54</v>
       </c>
       <c r="L52" s="23">
-        <v>376</v>
+        <v>255</v>
       </c>
       <c r="M52" s="24" t="s">
         <v>55</v>
@@ -7349,7 +7349,7 @@
         <v>54</v>
       </c>
       <c r="L53" s="30">
-        <v>354</v>
+        <v>335</v>
       </c>
       <c r="M53" s="31" t="s">
         <v>55</v>
@@ -7390,7 +7390,7 @@
         <v>54</v>
       </c>
       <c r="L54" s="23">
-        <v>107</v>
+        <v>452</v>
       </c>
       <c r="M54" s="24" t="s">
         <v>55</v>
@@ -7431,7 +7431,7 @@
         <v>54</v>
       </c>
       <c r="L55" s="30">
-        <v>130</v>
+        <v>401</v>
       </c>
       <c r="M55" s="31" t="s">
         <v>55</v>
@@ -7472,7 +7472,7 @@
         <v>54</v>
       </c>
       <c r="L56" s="23">
-        <v>477</v>
+        <v>111</v>
       </c>
       <c r="M56" s="24" t="s">
         <v>55</v>
@@ -7513,7 +7513,7 @@
         <v>54</v>
       </c>
       <c r="L57" s="30">
-        <v>152</v>
+        <v>467</v>
       </c>
       <c r="M57" s="31" t="s">
         <v>55</v>
@@ -7554,7 +7554,7 @@
         <v>54</v>
       </c>
       <c r="L58" s="23">
-        <v>448</v>
+        <v>403</v>
       </c>
       <c r="M58" s="24" t="s">
         <v>55</v>
@@ -7595,7 +7595,7 @@
         <v>54</v>
       </c>
       <c r="L59" s="30">
-        <v>241</v>
+        <v>421</v>
       </c>
       <c r="M59" s="31" t="s">
         <v>55</v>
@@ -7636,7 +7636,7 @@
         <v>54</v>
       </c>
       <c r="L60" s="23">
-        <v>98</v>
+        <v>334</v>
       </c>
       <c r="M60" s="24" t="s">
         <v>55</v>
@@ -7677,7 +7677,7 @@
         <v>54</v>
       </c>
       <c r="L61" s="30">
-        <v>167</v>
+        <v>488</v>
       </c>
       <c r="M61" s="31" t="s">
         <v>55</v>
@@ -7718,7 +7718,7 @@
         <v>54</v>
       </c>
       <c r="L62" s="23">
-        <v>553</v>
+        <v>458</v>
       </c>
       <c r="M62" s="24" t="s">
         <v>55</v>
@@ -7759,7 +7759,7 @@
         <v>54</v>
       </c>
       <c r="L63" s="30">
-        <v>453</v>
+        <v>224</v>
       </c>
       <c r="M63" s="31" t="s">
         <v>55</v>
@@ -7800,7 +7800,7 @@
         <v>54</v>
       </c>
       <c r="L64" s="23">
-        <v>436</v>
+        <v>534</v>
       </c>
       <c r="M64" s="24" t="s">
         <v>55</v>
@@ -7841,7 +7841,7 @@
         <v>54</v>
       </c>
       <c r="L65" s="30">
-        <v>431</v>
+        <v>234</v>
       </c>
       <c r="M65" s="31" t="s">
         <v>55</v>
@@ -7882,7 +7882,7 @@
         <v>54</v>
       </c>
       <c r="L66" s="23">
-        <v>452</v>
+        <v>98</v>
       </c>
       <c r="M66" s="24" t="s">
         <v>55</v>
@@ -7923,7 +7923,7 @@
         <v>54</v>
       </c>
       <c r="L67" s="30">
-        <v>289</v>
+        <v>246</v>
       </c>
       <c r="M67" s="31" t="s">
         <v>55</v>
@@ -7964,7 +7964,7 @@
         <v>54</v>
       </c>
       <c r="L68" s="23">
-        <v>433</v>
+        <v>211</v>
       </c>
       <c r="M68" s="24" t="s">
         <v>55</v>
@@ -8005,7 +8005,7 @@
         <v>54</v>
       </c>
       <c r="L69" s="30">
-        <v>370</v>
+        <v>490</v>
       </c>
       <c r="M69" s="31" t="s">
         <v>55</v>
@@ -8046,7 +8046,7 @@
         <v>54</v>
       </c>
       <c r="L70" s="23">
-        <v>155</v>
+        <v>272</v>
       </c>
       <c r="M70" s="24" t="s">
         <v>55</v>
@@ -8087,7 +8087,7 @@
         <v>54</v>
       </c>
       <c r="L71" s="30">
-        <v>95</v>
+        <v>285</v>
       </c>
       <c r="M71" s="31" t="s">
         <v>55</v>
@@ -8128,7 +8128,7 @@
         <v>54</v>
       </c>
       <c r="L72" s="23">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="M72" s="24" t="s">
         <v>55</v>
@@ -8169,7 +8169,7 @@
         <v>54</v>
       </c>
       <c r="L73" s="30">
-        <v>193</v>
+        <v>286</v>
       </c>
       <c r="M73" s="31" t="s">
         <v>55</v>
@@ -8210,7 +8210,7 @@
         <v>54</v>
       </c>
       <c r="L74" s="23">
-        <v>109</v>
+        <v>551</v>
       </c>
       <c r="M74" s="24" t="s">
         <v>55</v>
@@ -8251,7 +8251,7 @@
         <v>54</v>
       </c>
       <c r="L75" s="30">
-        <v>187</v>
+        <v>109</v>
       </c>
       <c r="M75" s="31" t="s">
         <v>55</v>
@@ -8292,7 +8292,7 @@
         <v>54</v>
       </c>
       <c r="L76" s="23">
-        <v>192</v>
+        <v>338</v>
       </c>
       <c r="M76" s="24" t="s">
         <v>55</v>
@@ -8333,7 +8333,7 @@
         <v>54</v>
       </c>
       <c r="L77" s="30">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="M77" s="31" t="s">
         <v>55</v>
@@ -8374,7 +8374,7 @@
         <v>54</v>
       </c>
       <c r="L78" s="23">
-        <v>445</v>
+        <v>373</v>
       </c>
       <c r="M78" s="24" t="s">
         <v>55</v>
@@ -8415,7 +8415,7 @@
         <v>54</v>
       </c>
       <c r="L79" s="30">
-        <v>235</v>
+        <v>449</v>
       </c>
       <c r="M79" s="31" t="s">
         <v>55</v>
@@ -8456,7 +8456,7 @@
         <v>54</v>
       </c>
       <c r="L80" s="23">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="M80" s="24" t="s">
         <v>55</v>
@@ -8497,21 +8497,21 @@
         <v>54</v>
       </c>
       <c r="L81" s="30">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="M81" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="82" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="16" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B82" s="17" t="s">
         <v>19</v>
       </c>
       <c r="C82" s="18" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D82" s="19" t="s">
         <v>47</v>
@@ -8526,7 +8526,7 @@
         <v>254</v>
       </c>
       <c r="H82" s="21" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I82" s="21" t="s">
         <v>256</v>
@@ -8538,21 +8538,21 @@
         <v>54</v>
       </c>
       <c r="L82" s="23">
-        <v>126</v>
+        <v>523</v>
       </c>
       <c r="M82" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="83" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B83" s="26" t="s">
         <v>19</v>
       </c>
       <c r="C83" s="27" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D83" s="32" t="s">
         <v>62</v>
@@ -8567,7 +8567,7 @@
         <v>260</v>
       </c>
       <c r="H83" s="29" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I83" s="29" t="s">
         <v>262</v>
@@ -8579,21 +8579,21 @@
         <v>54</v>
       </c>
       <c r="L83" s="30">
-        <v>87</v>
+        <v>535</v>
       </c>
       <c r="M83" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="84" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="16" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B84" s="17" t="s">
         <v>19</v>
       </c>
       <c r="C84" s="18" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D84" s="32" t="s">
         <v>62</v>
@@ -8608,7 +8608,7 @@
         <v>266</v>
       </c>
       <c r="H84" s="21" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I84" s="21" t="s">
         <v>268</v>
@@ -8620,21 +8620,21 @@
         <v>54</v>
       </c>
       <c r="L84" s="23">
-        <v>234</v>
+        <v>301</v>
       </c>
       <c r="M84" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="85" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="25" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B85" s="26" t="s">
         <v>19</v>
       </c>
       <c r="C85" s="27" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D85" s="32" t="s">
         <v>62</v>
@@ -8649,7 +8649,7 @@
         <v>272</v>
       </c>
       <c r="H85" s="29" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I85" s="29" t="s">
         <v>274</v>
@@ -8661,21 +8661,21 @@
         <v>54</v>
       </c>
       <c r="L85" s="30">
-        <v>349</v>
+        <v>406</v>
       </c>
       <c r="M85" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="86" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="16" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B86" s="17" t="s">
         <v>19</v>
       </c>
       <c r="C86" s="18" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D86" s="32" t="s">
         <v>62</v>
@@ -8690,7 +8690,7 @@
         <v>278</v>
       </c>
       <c r="H86" s="21" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="I86" s="21" t="s">
         <v>280</v>
@@ -8702,21 +8702,21 @@
         <v>54</v>
       </c>
       <c r="L86" s="23">
-        <v>257</v>
+        <v>130</v>
       </c>
       <c r="M86" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="87" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="25" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B87" s="26" t="s">
         <v>19</v>
       </c>
       <c r="C87" s="27" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D87" s="32" t="s">
         <v>67</v>
@@ -8731,7 +8731,7 @@
         <v>284</v>
       </c>
       <c r="H87" s="29" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="I87" s="29" t="s">
         <v>286</v>
@@ -8743,21 +8743,21 @@
         <v>54</v>
       </c>
       <c r="L87" s="30">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="M87" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="88" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="16" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B88" s="17" t="s">
         <v>19</v>
       </c>
       <c r="C88" s="18" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D88" s="32" t="s">
         <v>62</v>
@@ -8772,7 +8772,7 @@
         <v>290</v>
       </c>
       <c r="H88" s="21" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I88" s="21" t="s">
         <v>292</v>
@@ -8784,21 +8784,21 @@
         <v>54</v>
       </c>
       <c r="L88" s="23">
-        <v>79</v>
+        <v>190</v>
       </c>
       <c r="M88" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="89" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="25" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B89" s="26" t="s">
         <v>19</v>
       </c>
       <c r="C89" s="27" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D89" s="32" t="s">
         <v>67</v>
@@ -8813,7 +8813,7 @@
         <v>296</v>
       </c>
       <c r="H89" s="29" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="I89" s="29" t="s">
         <v>298</v>
@@ -8825,21 +8825,21 @@
         <v>54</v>
       </c>
       <c r="L89" s="30">
-        <v>255</v>
+        <v>423</v>
       </c>
       <c r="M89" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="90" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="16" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B90" s="17" t="s">
         <v>19</v>
       </c>
       <c r="C90" s="18" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D90" s="32" t="s">
         <v>67</v>
@@ -8854,7 +8854,7 @@
         <v>302</v>
       </c>
       <c r="H90" s="21" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="I90" s="21" t="s">
         <v>304</v>
@@ -8866,21 +8866,21 @@
         <v>54</v>
       </c>
       <c r="L90" s="23">
-        <v>287</v>
+        <v>146</v>
       </c>
       <c r="M90" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="91" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="25" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B91" s="26" t="s">
         <v>19</v>
       </c>
       <c r="C91" s="27" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D91" s="32" t="s">
         <v>67</v>
@@ -8895,7 +8895,7 @@
         <v>308</v>
       </c>
       <c r="H91" s="29" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I91" s="29" t="s">
         <v>310</v>
@@ -8907,21 +8907,21 @@
         <v>54</v>
       </c>
       <c r="L91" s="30">
-        <v>220</v>
+        <v>454</v>
       </c>
       <c r="M91" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="92" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="16" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B92" s="17" t="s">
         <v>19</v>
       </c>
       <c r="C92" s="18" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D92" s="19" t="s">
         <v>47</v>
@@ -8936,7 +8936,7 @@
         <v>314</v>
       </c>
       <c r="H92" s="21" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="I92" s="21" t="s">
         <v>316</v>
@@ -8948,21 +8948,21 @@
         <v>54</v>
       </c>
       <c r="L92" s="23">
-        <v>186</v>
+        <v>131</v>
       </c>
       <c r="M92" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="93" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="25" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B93" s="26" t="s">
         <v>19</v>
       </c>
       <c r="C93" s="27" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D93" s="32" t="s">
         <v>62</v>
@@ -8977,7 +8977,7 @@
         <v>320</v>
       </c>
       <c r="H93" s="29" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I93" s="29" t="s">
         <v>322</v>
@@ -8989,21 +8989,21 @@
         <v>54</v>
       </c>
       <c r="L93" s="30">
-        <v>449</v>
+        <v>414</v>
       </c>
       <c r="M93" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="94" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="16" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B94" s="17" t="s">
         <v>19</v>
       </c>
       <c r="C94" s="18" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D94" s="32" t="s">
         <v>62</v>
@@ -9018,7 +9018,7 @@
         <v>326</v>
       </c>
       <c r="H94" s="21" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I94" s="21" t="s">
         <v>328</v>
@@ -9030,21 +9030,21 @@
         <v>54</v>
       </c>
       <c r="L94" s="23">
-        <v>165</v>
+        <v>496</v>
       </c>
       <c r="M94" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="95" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="25" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B95" s="26" t="s">
         <v>19</v>
       </c>
       <c r="C95" s="27" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D95" s="32" t="s">
         <v>67</v>
@@ -9059,7 +9059,7 @@
         <v>332</v>
       </c>
       <c r="H95" s="29" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I95" s="29" t="s">
         <v>334</v>
@@ -9071,21 +9071,21 @@
         <v>54</v>
       </c>
       <c r="L95" s="30">
-        <v>478</v>
+        <v>314</v>
       </c>
       <c r="M95" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="96" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="16" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B96" s="17" t="s">
         <v>19</v>
       </c>
       <c r="C96" s="18" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D96" s="32" t="s">
         <v>67</v>
@@ -9100,7 +9100,7 @@
         <v>338</v>
       </c>
       <c r="H96" s="21" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="I96" s="21" t="s">
         <v>340</v>
@@ -9112,1732 +9112,1732 @@
         <v>54</v>
       </c>
       <c r="L96" s="23">
-        <v>251</v>
+        <v>490</v>
       </c>
       <c r="M96" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="97" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="25" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B97" s="26" t="s">
         <v>21</v>
       </c>
       <c r="C97" s="27" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D97" s="19" t="s">
         <v>47</v>
       </c>
       <c r="E97" s="28" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F97" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G97" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H97" s="29" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="I97" s="29" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J97" s="29" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K97" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L97" s="30">
-        <v>265</v>
+        <v>472</v>
       </c>
       <c r="M97" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="98" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="16" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B98" s="17" t="s">
         <v>21</v>
       </c>
       <c r="C98" s="18" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D98" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E98" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F98" s="21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G98" s="21" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H98" s="21" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="I98" s="21" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J98" s="21" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K98" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L98" s="23">
-        <v>288</v>
+        <v>395</v>
       </c>
       <c r="M98" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="99" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="25" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B99" s="26" t="s">
         <v>21</v>
       </c>
       <c r="C99" s="27" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D99" s="32" t="s">
         <v>67</v>
       </c>
       <c r="E99" s="28" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F99" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G99" s="29" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H99" s="29" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I99" s="29" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J99" s="29" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K99" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L99" s="30">
-        <v>406</v>
+        <v>431</v>
       </c>
       <c r="M99" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="100" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="16" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B100" s="17" t="s">
         <v>21</v>
       </c>
       <c r="C100" s="18" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D100" s="32" t="s">
         <v>67</v>
       </c>
       <c r="E100" s="20" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F100" s="21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G100" s="21" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H100" s="21" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="I100" s="21" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J100" s="21" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K100" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L100" s="23">
-        <v>479</v>
+        <v>389</v>
       </c>
       <c r="M100" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="101" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="25" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B101" s="26" t="s">
         <v>21</v>
       </c>
       <c r="C101" s="27" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D101" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E101" s="28" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F101" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G101" s="29" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H101" s="29" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I101" s="29" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="J101" s="29" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K101" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L101" s="30">
-        <v>289</v>
+        <v>162</v>
       </c>
       <c r="M101" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="102" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="16" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B102" s="17" t="s">
         <v>21</v>
       </c>
       <c r="C102" s="18" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D102" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E102" s="20" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F102" s="21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G102" s="21" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H102" s="21" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="I102" s="21" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J102" s="21" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K102" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L102" s="23">
-        <v>379</v>
+        <v>230</v>
       </c>
       <c r="M102" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="103" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="25" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B103" s="26" t="s">
         <v>21</v>
       </c>
       <c r="C103" s="27" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D103" s="32" t="s">
         <v>67</v>
       </c>
       <c r="E103" s="28" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F103" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G103" s="29" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H103" s="29" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I103" s="29" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J103" s="29" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K103" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L103" s="30">
+        <v>384</v>
+      </c>
+      <c r="M103" s="31" t="s">
         <v>386</v>
-      </c>
-      <c r="M103" s="31" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="104" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="16" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B104" s="17" t="s">
         <v>21</v>
       </c>
       <c r="C104" s="18" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D104" s="32" t="s">
         <v>92</v>
       </c>
       <c r="E104" s="20" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F104" s="21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G104" s="21" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H104" s="21" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I104" s="21" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J104" s="21" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K104" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L104" s="23">
-        <v>540</v>
+        <v>409</v>
       </c>
       <c r="M104" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="105" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="25" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B105" s="26" t="s">
         <v>21</v>
       </c>
       <c r="C105" s="27" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D105" s="19" t="s">
         <v>47</v>
       </c>
       <c r="E105" s="28" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F105" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G105" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H105" s="29" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="I105" s="29" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J105" s="29" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K105" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L105" s="30">
-        <v>438</v>
+        <v>270</v>
       </c>
       <c r="M105" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="106" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="16" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B106" s="17" t="s">
         <v>21</v>
       </c>
       <c r="C106" s="18" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D106" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E106" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F106" s="21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G106" s="21" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H106" s="21" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="I106" s="21" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J106" s="21" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K106" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L106" s="23">
-        <v>402</v>
+        <v>115</v>
       </c>
       <c r="M106" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="107" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="25" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B107" s="26" t="s">
         <v>21</v>
       </c>
       <c r="C107" s="27" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D107" s="32" t="s">
         <v>67</v>
       </c>
       <c r="E107" s="28" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F107" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G107" s="29" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H107" s="29" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="I107" s="29" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J107" s="29" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K107" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L107" s="30">
-        <v>378</v>
+        <v>125</v>
       </c>
       <c r="M107" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="108" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="16" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B108" s="17" t="s">
         <v>21</v>
       </c>
       <c r="C108" s="18" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D108" s="32" t="s">
         <v>67</v>
       </c>
       <c r="E108" s="20" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F108" s="21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G108" s="21" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H108" s="21" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="I108" s="21" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J108" s="21" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K108" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L108" s="23">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="M108" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="109" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="25" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B109" s="26" t="s">
         <v>21</v>
       </c>
       <c r="C109" s="27" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D109" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E109" s="28" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F109" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G109" s="29" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H109" s="29" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="I109" s="29" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="J109" s="29" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K109" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L109" s="30">
-        <v>258</v>
+        <v>198</v>
       </c>
       <c r="M109" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="110" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="16" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B110" s="17" t="s">
         <v>21</v>
       </c>
       <c r="C110" s="18" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D110" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E110" s="20" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F110" s="21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G110" s="21" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H110" s="21" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I110" s="21" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J110" s="21" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K110" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L110" s="23">
-        <v>382</v>
+        <v>303</v>
       </c>
       <c r="M110" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="111" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="25" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B111" s="26" t="s">
         <v>21</v>
       </c>
       <c r="C111" s="27" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D111" s="32" t="s">
         <v>67</v>
       </c>
       <c r="E111" s="28" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F111" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G111" s="29" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H111" s="29" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="I111" s="29" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J111" s="29" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K111" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L111" s="30">
-        <v>464</v>
+        <v>541</v>
       </c>
       <c r="M111" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="112" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="16" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B112" s="17" t="s">
         <v>21</v>
       </c>
       <c r="C112" s="18" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D112" s="32" t="s">
         <v>92</v>
       </c>
       <c r="E112" s="20" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F112" s="21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G112" s="21" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H112" s="21" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I112" s="21" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J112" s="21" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K112" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L112" s="23">
-        <v>266</v>
+        <v>357</v>
       </c>
       <c r="M112" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="113" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="25" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B113" s="26" t="s">
         <v>21</v>
       </c>
       <c r="C113" s="27" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D113" s="19" t="s">
         <v>47</v>
       </c>
       <c r="E113" s="28" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F113" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G113" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H113" s="29" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="I113" s="29" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J113" s="29" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K113" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L113" s="30">
-        <v>450</v>
+        <v>476</v>
       </c>
       <c r="M113" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="114" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="16" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B114" s="17" t="s">
         <v>21</v>
       </c>
       <c r="C114" s="18" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D114" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E114" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F114" s="21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G114" s="21" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H114" s="21" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="I114" s="21" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J114" s="21" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K114" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L114" s="23">
-        <v>437</v>
+        <v>297</v>
       </c>
       <c r="M114" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="115" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="25" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B115" s="26" t="s">
         <v>21</v>
       </c>
       <c r="C115" s="27" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D115" s="32" t="s">
         <v>67</v>
       </c>
       <c r="E115" s="28" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F115" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G115" s="29" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H115" s="29" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="I115" s="29" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J115" s="29" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K115" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L115" s="30">
-        <v>355</v>
+        <v>394</v>
       </c>
       <c r="M115" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="116" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="16" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B116" s="17" t="s">
         <v>21</v>
       </c>
       <c r="C116" s="18" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D116" s="32" t="s">
         <v>67</v>
       </c>
       <c r="E116" s="20" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F116" s="21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G116" s="21" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H116" s="21" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="I116" s="21" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J116" s="21" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K116" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L116" s="23">
-        <v>480</v>
+        <v>398</v>
       </c>
       <c r="M116" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="117" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="25" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B117" s="26" t="s">
         <v>21</v>
       </c>
       <c r="C117" s="27" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D117" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E117" s="28" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F117" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G117" s="29" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H117" s="29" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="I117" s="29" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="J117" s="29" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K117" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L117" s="30">
-        <v>141</v>
+        <v>221</v>
       </c>
       <c r="M117" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="118" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="16" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B118" s="17" t="s">
         <v>21</v>
       </c>
       <c r="C118" s="18" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D118" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E118" s="20" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F118" s="21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G118" s="21" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H118" s="21" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="I118" s="21" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J118" s="21" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K118" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L118" s="23">
-        <v>228</v>
+        <v>443</v>
       </c>
       <c r="M118" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="119" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="25" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B119" s="26" t="s">
         <v>21</v>
       </c>
       <c r="C119" s="27" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D119" s="32" t="s">
         <v>67</v>
       </c>
       <c r="E119" s="28" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F119" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G119" s="29" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H119" s="29" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="I119" s="29" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J119" s="29" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K119" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L119" s="30">
-        <v>382</v>
+        <v>125</v>
       </c>
       <c r="M119" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="120" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="16" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B120" s="17" t="s">
         <v>21</v>
       </c>
       <c r="C120" s="18" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D120" s="32" t="s">
         <v>92</v>
       </c>
       <c r="E120" s="20" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F120" s="21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G120" s="21" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H120" s="21" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I120" s="21" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J120" s="21" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K120" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L120" s="23">
-        <v>513</v>
+        <v>266</v>
       </c>
       <c r="M120" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="25" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B121" s="26" t="s">
         <v>21</v>
       </c>
       <c r="C121" s="27" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D121" s="19" t="s">
         <v>47</v>
       </c>
       <c r="E121" s="28" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F121" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G121" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H121" s="29" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="I121" s="29" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J121" s="29" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K121" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L121" s="30">
-        <v>375</v>
+        <v>481</v>
       </c>
       <c r="M121" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" s="16" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B122" s="17" t="s">
         <v>21</v>
       </c>
       <c r="C122" s="18" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D122" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E122" s="20" t="s">
+        <v>441</v>
+      </c>
+      <c r="F122" s="21" t="s">
+        <v>435</v>
+      </c>
+      <c r="G122" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="H122" s="21" t="s">
+        <v>534</v>
+      </c>
+      <c r="I122" s="21" t="s">
+        <v>444</v>
+      </c>
+      <c r="J122" s="21" t="s">
+        <v>444</v>
+      </c>
+      <c r="K122" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="L122" s="23">
         <v>440</v>
       </c>
-      <c r="F122" s="21" t="s">
-        <v>434</v>
-      </c>
-      <c r="G122" s="21" t="s">
-        <v>441</v>
-      </c>
-      <c r="H122" s="21" t="s">
-        <v>533</v>
-      </c>
-      <c r="I122" s="21" t="s">
-        <v>443</v>
-      </c>
-      <c r="J122" s="21" t="s">
-        <v>443</v>
-      </c>
-      <c r="K122" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L122" s="23">
-        <v>498</v>
-      </c>
       <c r="M122" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="25" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B123" s="26" t="s">
         <v>21</v>
       </c>
       <c r="C123" s="27" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D123" s="32" t="s">
         <v>67</v>
       </c>
       <c r="E123" s="28" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F123" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G123" s="29" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H123" s="29" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="I123" s="29" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J123" s="29" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K123" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L123" s="30">
-        <v>300</v>
+        <v>185</v>
       </c>
       <c r="M123" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" s="16" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B124" s="17" t="s">
         <v>21</v>
       </c>
       <c r="C124" s="18" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D124" s="32" t="s">
         <v>67</v>
       </c>
       <c r="E124" s="20" t="s">
+        <v>453</v>
+      </c>
+      <c r="F124" s="21" t="s">
+        <v>435</v>
+      </c>
+      <c r="G124" s="21" t="s">
+        <v>454</v>
+      </c>
+      <c r="H124" s="21" t="s">
+        <v>540</v>
+      </c>
+      <c r="I124" s="21" t="s">
+        <v>456</v>
+      </c>
+      <c r="J124" s="21" t="s">
+        <v>456</v>
+      </c>
+      <c r="K124" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="L124" s="23">
         <v>452</v>
       </c>
-      <c r="F124" s="21" t="s">
-        <v>434</v>
-      </c>
-      <c r="G124" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="H124" s="21" t="s">
-        <v>539</v>
-      </c>
-      <c r="I124" s="21" t="s">
-        <v>455</v>
-      </c>
-      <c r="J124" s="21" t="s">
-        <v>455</v>
-      </c>
-      <c r="K124" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="L124" s="23">
-        <v>513</v>
-      </c>
       <c r="M124" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="125" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="25" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B125" s="26" t="s">
         <v>21</v>
       </c>
       <c r="C125" s="27" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D125" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E125" s="28" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F125" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G125" s="29" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H125" s="29" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="I125" s="29" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="J125" s="29" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K125" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L125" s="30">
-        <v>258</v>
+        <v>343</v>
       </c>
       <c r="M125" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="126" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" s="16" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B126" s="17" t="s">
         <v>21</v>
       </c>
       <c r="C126" s="18" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D126" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E126" s="20" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F126" s="21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G126" s="21" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H126" s="21" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I126" s="21" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J126" s="21" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K126" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L126" s="23">
-        <v>155</v>
+        <v>121</v>
       </c>
       <c r="M126" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="127" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" s="25" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B127" s="26" t="s">
         <v>21</v>
       </c>
       <c r="C127" s="27" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D127" s="32" t="s">
         <v>67</v>
       </c>
       <c r="E127" s="28" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F127" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G127" s="29" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H127" s="29" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="I127" s="29" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J127" s="29" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K127" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L127" s="30">
-        <v>348</v>
+        <v>251</v>
       </c>
       <c r="M127" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="128" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" s="16" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B128" s="17" t="s">
         <v>21</v>
       </c>
       <c r="C128" s="18" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D128" s="32" t="s">
         <v>92</v>
       </c>
       <c r="E128" s="20" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F128" s="21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G128" s="21" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H128" s="21" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="I128" s="21" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J128" s="21" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K128" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L128" s="23">
-        <v>508</v>
+        <v>177</v>
       </c>
       <c r="M128" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="129" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" s="25" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B129" s="26" t="s">
         <v>21</v>
       </c>
       <c r="C129" s="27" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D129" s="19" t="s">
         <v>47</v>
       </c>
       <c r="E129" s="28" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F129" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G129" s="29" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H129" s="29" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="I129" s="29" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J129" s="29" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K129" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L129" s="30">
-        <v>371</v>
+        <v>484</v>
       </c>
       <c r="M129" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="130" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="16" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B130" s="17" t="s">
         <v>21</v>
       </c>
       <c r="C130" s="18" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D130" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E130" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F130" s="21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G130" s="21" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H130" s="21" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="I130" s="21" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J130" s="21" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K130" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L130" s="23">
-        <v>368</v>
+        <v>109</v>
       </c>
       <c r="M130" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="131" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="25" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B131" s="26" t="s">
         <v>21</v>
       </c>
       <c r="C131" s="27" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D131" s="32" t="s">
         <v>67</v>
       </c>
       <c r="E131" s="28" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F131" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G131" s="29" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H131" s="29" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="I131" s="29" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J131" s="29" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K131" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L131" s="30">
-        <v>242</v>
+        <v>471</v>
       </c>
       <c r="M131" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="132" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" s="16" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B132" s="17" t="s">
         <v>21</v>
       </c>
       <c r="C132" s="18" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D132" s="32" t="s">
         <v>67</v>
       </c>
       <c r="E132" s="20" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F132" s="21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G132" s="21" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H132" s="21" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="I132" s="21" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J132" s="21" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K132" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L132" s="23">
-        <v>456</v>
+        <v>246</v>
       </c>
       <c r="M132" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="133" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" s="25" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B133" s="26" t="s">
         <v>21</v>
       </c>
       <c r="C133" s="27" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D133" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E133" s="28" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F133" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G133" s="29" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H133" s="29" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I133" s="29" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="J133" s="29" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K133" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L133" s="30">
-        <v>259</v>
+        <v>467</v>
       </c>
       <c r="M133" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="134" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" s="16" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B134" s="17" t="s">
         <v>21</v>
       </c>
       <c r="C134" s="18" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D134" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E134" s="20" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F134" s="21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G134" s="21" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H134" s="21" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="I134" s="21" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J134" s="21" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K134" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L134" s="23">
-        <v>211</v>
+        <v>166</v>
       </c>
       <c r="M134" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="135" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" s="25" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B135" s="26" t="s">
         <v>21</v>
       </c>
       <c r="C135" s="27" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D135" s="32" t="s">
         <v>67</v>
       </c>
       <c r="E135" s="28" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F135" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G135" s="29" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H135" s="29" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I135" s="29" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J135" s="29" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K135" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L135" s="30">
-        <v>451</v>
+        <v>549</v>
       </c>
       <c r="M135" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="136" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" s="16" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B136" s="17" t="s">
         <v>21</v>
       </c>
       <c r="C136" s="18" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D136" s="32" t="s">
         <v>92</v>
       </c>
       <c r="E136" s="20" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F136" s="21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G136" s="21" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H136" s="21" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="I136" s="21" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J136" s="21" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K136" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L136" s="23">
-        <v>281</v>
+        <v>467</v>
       </c>
       <c r="M136" s="24" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="137" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" s="25" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B137" s="26" t="s">
         <v>23</v>
       </c>
       <c r="C137" s="27" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D137" s="32" t="s">
         <v>67</v>
       </c>
       <c r="E137" s="28" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F137" s="29" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G137" s="29" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H137" s="29" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="I137" s="29" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="J137" s="29" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="K137" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L137" s="30">
-        <v>359</v>
+        <v>332</v>
       </c>
       <c r="M137" s="31" t="s">
-        <v>55</v>
+        <v>386</v>
       </c>
     </row>
     <row r="138" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" s="16" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B138" s="17" t="s">
         <v>23</v>
       </c>
       <c r="C138" s="18" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D138" s="32" t="s">
         <v>92</v>
       </c>
       <c r="E138" s="20" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F138" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G138" s="21" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H138" s="21" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="I138" s="21" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="J138" s="21" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="K138" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L138" s="23">
-        <v>519</v>
+        <v>330</v>
       </c>
       <c r="M138" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="139" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10857,7 +10857,7 @@
         <v>592</v>
       </c>
       <c r="F139" s="29" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G139" s="29" t="s">
         <v>593</v>
@@ -10875,10 +10875,10 @@
         <v>54</v>
       </c>
       <c r="L139" s="30">
-        <v>508</v>
+        <v>78</v>
       </c>
       <c r="M139" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="140" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10898,7 +10898,7 @@
         <v>598</v>
       </c>
       <c r="F140" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G140" s="21" t="s">
         <v>599</v>
@@ -10916,10 +10916,10 @@
         <v>54</v>
       </c>
       <c r="L140" s="23">
-        <v>480</v>
+        <v>459</v>
       </c>
       <c r="M140" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="141" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10939,7 +10939,7 @@
         <v>604</v>
       </c>
       <c r="F141" s="29" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G141" s="29" t="s">
         <v>605</v>
@@ -10957,10 +10957,10 @@
         <v>54</v>
       </c>
       <c r="L141" s="30">
-        <v>360</v>
+        <v>298</v>
       </c>
       <c r="M141" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="142" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10980,7 +10980,7 @@
         <v>610</v>
       </c>
       <c r="F142" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G142" s="21" t="s">
         <v>611</v>
@@ -10998,10 +10998,10 @@
         <v>54</v>
       </c>
       <c r="L142" s="23">
-        <v>352</v>
+        <v>428</v>
       </c>
       <c r="M142" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="143" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11021,7 +11021,7 @@
         <v>616</v>
       </c>
       <c r="F143" s="29" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G143" s="29" t="s">
         <v>617</v>
@@ -11039,10 +11039,10 @@
         <v>54</v>
       </c>
       <c r="L143" s="30">
-        <v>102</v>
+        <v>539</v>
       </c>
       <c r="M143" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="144" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11062,7 +11062,7 @@
         <v>622</v>
       </c>
       <c r="F144" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G144" s="21" t="s">
         <v>623</v>
@@ -11080,10 +11080,10 @@
         <v>54</v>
       </c>
       <c r="L144" s="23">
-        <v>352</v>
+        <v>526</v>
       </c>
       <c r="M144" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="145" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11103,7 +11103,7 @@
         <v>628</v>
       </c>
       <c r="F145" s="29" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G145" s="29" t="s">
         <v>629</v>
@@ -11121,10 +11121,10 @@
         <v>54</v>
       </c>
       <c r="L145" s="30">
-        <v>457</v>
+        <v>291</v>
       </c>
       <c r="M145" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="146" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11144,7 +11144,7 @@
         <v>634</v>
       </c>
       <c r="F146" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G146" s="21" t="s">
         <v>635</v>
@@ -11162,10 +11162,10 @@
         <v>54</v>
       </c>
       <c r="L146" s="23">
-        <v>269</v>
+        <v>178</v>
       </c>
       <c r="M146" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="147" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11185,7 +11185,7 @@
         <v>640</v>
       </c>
       <c r="F147" s="29" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G147" s="29" t="s">
         <v>641</v>
@@ -11203,10 +11203,10 @@
         <v>54</v>
       </c>
       <c r="L147" s="30">
-        <v>197</v>
+        <v>354</v>
       </c>
       <c r="M147" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="148" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11223,31 +11223,31 @@
         <v>67</v>
       </c>
       <c r="E148" s="20" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F148" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G148" s="21" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H148" s="21" t="s">
         <v>646</v>
       </c>
       <c r="I148" s="21" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="J148" s="21" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="K148" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L148" s="23">
-        <v>457</v>
+        <v>207</v>
       </c>
       <c r="M148" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="149" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11264,31 +11264,31 @@
         <v>92</v>
       </c>
       <c r="E149" s="28" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F149" s="29" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G149" s="29" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H149" s="29" t="s">
         <v>649</v>
       </c>
       <c r="I149" s="29" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="J149" s="29" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="K149" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L149" s="30">
-        <v>413</v>
+        <v>128</v>
       </c>
       <c r="M149" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="150" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11308,7 +11308,7 @@
         <v>592</v>
       </c>
       <c r="F150" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G150" s="21" t="s">
         <v>593</v>
@@ -11326,10 +11326,10 @@
         <v>54</v>
       </c>
       <c r="L150" s="23">
-        <v>146</v>
+        <v>514</v>
       </c>
       <c r="M150" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="151" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11349,7 +11349,7 @@
         <v>598</v>
       </c>
       <c r="F151" s="29" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G151" s="29" t="s">
         <v>599</v>
@@ -11367,10 +11367,10 @@
         <v>54</v>
       </c>
       <c r="L151" s="30">
-        <v>109</v>
+        <v>507</v>
       </c>
       <c r="M151" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="152" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11390,7 +11390,7 @@
         <v>604</v>
       </c>
       <c r="F152" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G152" s="21" t="s">
         <v>605</v>
@@ -11408,10 +11408,10 @@
         <v>54</v>
       </c>
       <c r="L152" s="23">
-        <v>145</v>
+        <v>361</v>
       </c>
       <c r="M152" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="153" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11431,7 +11431,7 @@
         <v>610</v>
       </c>
       <c r="F153" s="29" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G153" s="29" t="s">
         <v>611</v>
@@ -11449,10 +11449,10 @@
         <v>54</v>
       </c>
       <c r="L153" s="30">
-        <v>554</v>
+        <v>237</v>
       </c>
       <c r="M153" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="154" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11472,7 +11472,7 @@
         <v>616</v>
       </c>
       <c r="F154" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G154" s="21" t="s">
         <v>617</v>
@@ -11490,10 +11490,10 @@
         <v>54</v>
       </c>
       <c r="L154" s="23">
-        <v>362</v>
+        <v>149</v>
       </c>
       <c r="M154" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="155" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11513,7 +11513,7 @@
         <v>622</v>
       </c>
       <c r="F155" s="29" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G155" s="29" t="s">
         <v>623</v>
@@ -11531,10 +11531,10 @@
         <v>54</v>
       </c>
       <c r="L155" s="30">
-        <v>221</v>
+        <v>163</v>
       </c>
       <c r="M155" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="156" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11554,7 +11554,7 @@
         <v>628</v>
       </c>
       <c r="F156" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G156" s="21" t="s">
         <v>629</v>
@@ -11572,10 +11572,10 @@
         <v>54</v>
       </c>
       <c r="L156" s="23">
-        <v>282</v>
+        <v>554</v>
       </c>
       <c r="M156" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="157" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11595,7 +11595,7 @@
         <v>634</v>
       </c>
       <c r="F157" s="29" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G157" s="29" t="s">
         <v>635</v>
@@ -11613,10 +11613,10 @@
         <v>54</v>
       </c>
       <c r="L157" s="30">
-        <v>309</v>
+        <v>121</v>
       </c>
       <c r="M157" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="158" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11636,7 +11636,7 @@
         <v>640</v>
       </c>
       <c r="F158" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G158" s="21" t="s">
         <v>641</v>
@@ -11654,10 +11654,10 @@
         <v>54</v>
       </c>
       <c r="L158" s="23">
-        <v>217</v>
+        <v>328</v>
       </c>
       <c r="M158" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="159" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11674,31 +11674,31 @@
         <v>67</v>
       </c>
       <c r="E159" s="28" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F159" s="29" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G159" s="29" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H159" s="29" t="s">
         <v>679</v>
       </c>
       <c r="I159" s="29" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="J159" s="29" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="K159" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L159" s="30">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="M159" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="160" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11715,31 +11715,31 @@
         <v>92</v>
       </c>
       <c r="E160" s="20" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F160" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G160" s="21" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H160" s="21" t="s">
         <v>682</v>
       </c>
       <c r="I160" s="21" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="J160" s="21" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="K160" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L160" s="23">
-        <v>155</v>
+        <v>323</v>
       </c>
       <c r="M160" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="161" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11759,7 +11759,7 @@
         <v>592</v>
       </c>
       <c r="F161" s="29" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G161" s="29" t="s">
         <v>593</v>
@@ -11777,10 +11777,10 @@
         <v>54</v>
       </c>
       <c r="L161" s="30">
-        <v>492</v>
+        <v>424</v>
       </c>
       <c r="M161" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="162" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11800,7 +11800,7 @@
         <v>598</v>
       </c>
       <c r="F162" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G162" s="21" t="s">
         <v>599</v>
@@ -11818,10 +11818,10 @@
         <v>54</v>
       </c>
       <c r="L162" s="23">
-        <v>262</v>
+        <v>446</v>
       </c>
       <c r="M162" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="163" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11841,7 +11841,7 @@
         <v>604</v>
       </c>
       <c r="F163" s="29" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G163" s="29" t="s">
         <v>605</v>
@@ -11859,10 +11859,10 @@
         <v>54</v>
       </c>
       <c r="L163" s="30">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="M163" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="164" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11882,7 +11882,7 @@
         <v>610</v>
       </c>
       <c r="F164" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G164" s="21" t="s">
         <v>611</v>
@@ -11900,10 +11900,10 @@
         <v>54</v>
       </c>
       <c r="L164" s="23">
-        <v>553</v>
+        <v>298</v>
       </c>
       <c r="M164" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="165" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11923,7 +11923,7 @@
         <v>616</v>
       </c>
       <c r="F165" s="29" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G165" s="29" t="s">
         <v>617</v>
@@ -11941,10 +11941,10 @@
         <v>54</v>
       </c>
       <c r="L165" s="30">
-        <v>249</v>
+        <v>285</v>
       </c>
       <c r="M165" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="166" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -11964,7 +11964,7 @@
         <v>622</v>
       </c>
       <c r="F166" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G166" s="21" t="s">
         <v>623</v>
@@ -11982,10 +11982,10 @@
         <v>54</v>
       </c>
       <c r="L166" s="23">
-        <v>398</v>
+        <v>510</v>
       </c>
       <c r="M166" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="167" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12005,7 +12005,7 @@
         <v>628</v>
       </c>
       <c r="F167" s="29" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G167" s="29" t="s">
         <v>629</v>
@@ -12023,10 +12023,10 @@
         <v>54</v>
       </c>
       <c r="L167" s="30">
-        <v>462</v>
+        <v>369</v>
       </c>
       <c r="M167" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="168" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12046,7 +12046,7 @@
         <v>634</v>
       </c>
       <c r="F168" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G168" s="21" t="s">
         <v>635</v>
@@ -12064,10 +12064,10 @@
         <v>54</v>
       </c>
       <c r="L168" s="23">
-        <v>450</v>
+        <v>370</v>
       </c>
       <c r="M168" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="169" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12087,7 +12087,7 @@
         <v>640</v>
       </c>
       <c r="F169" s="29" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G169" s="29" t="s">
         <v>641</v>
@@ -12105,10 +12105,10 @@
         <v>54</v>
       </c>
       <c r="L169" s="30">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="M169" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="170" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12125,31 +12125,31 @@
         <v>67</v>
       </c>
       <c r="E170" s="20" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F170" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G170" s="21" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H170" s="21" t="s">
         <v>712</v>
       </c>
       <c r="I170" s="21" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="J170" s="21" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="K170" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L170" s="23">
-        <v>522</v>
+        <v>451</v>
       </c>
       <c r="M170" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="171" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12166,31 +12166,31 @@
         <v>92</v>
       </c>
       <c r="E171" s="28" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F171" s="29" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G171" s="29" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H171" s="29" t="s">
         <v>715</v>
       </c>
       <c r="I171" s="29" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="J171" s="29" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="K171" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L171" s="30">
-        <v>181</v>
+        <v>327</v>
       </c>
       <c r="M171" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="172" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12210,7 +12210,7 @@
         <v>592</v>
       </c>
       <c r="F172" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G172" s="21" t="s">
         <v>593</v>
@@ -12228,10 +12228,10 @@
         <v>54</v>
       </c>
       <c r="L172" s="23">
-        <v>148</v>
+        <v>413</v>
       </c>
       <c r="M172" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="173" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12251,7 +12251,7 @@
         <v>598</v>
       </c>
       <c r="F173" s="29" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G173" s="29" t="s">
         <v>599</v>
@@ -12269,10 +12269,10 @@
         <v>54</v>
       </c>
       <c r="L173" s="30">
-        <v>258</v>
+        <v>477</v>
       </c>
       <c r="M173" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="174" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12292,7 +12292,7 @@
         <v>604</v>
       </c>
       <c r="F174" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G174" s="21" t="s">
         <v>605</v>
@@ -12310,10 +12310,10 @@
         <v>54</v>
       </c>
       <c r="L174" s="23">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="M174" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="175" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12333,7 +12333,7 @@
         <v>610</v>
       </c>
       <c r="F175" s="29" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G175" s="29" t="s">
         <v>611</v>
@@ -12351,10 +12351,10 @@
         <v>54</v>
       </c>
       <c r="L175" s="30">
-        <v>167</v>
+        <v>441</v>
       </c>
       <c r="M175" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="176" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12374,7 +12374,7 @@
         <v>616</v>
       </c>
       <c r="F176" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G176" s="21" t="s">
         <v>617</v>
@@ -12392,10 +12392,10 @@
         <v>54</v>
       </c>
       <c r="L176" s="23">
-        <v>343</v>
+        <v>129</v>
       </c>
       <c r="M176" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="177" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12415,7 +12415,7 @@
         <v>622</v>
       </c>
       <c r="F177" s="29" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G177" s="29" t="s">
         <v>623</v>
@@ -12433,10 +12433,10 @@
         <v>54</v>
       </c>
       <c r="L177" s="30">
-        <v>490</v>
+        <v>90</v>
       </c>
       <c r="M177" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="178" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12456,7 +12456,7 @@
         <v>628</v>
       </c>
       <c r="F178" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G178" s="21" t="s">
         <v>629</v>
@@ -12474,10 +12474,10 @@
         <v>54</v>
       </c>
       <c r="L178" s="23">
-        <v>483</v>
+        <v>536</v>
       </c>
       <c r="M178" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="179" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12497,7 +12497,7 @@
         <v>634</v>
       </c>
       <c r="F179" s="29" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G179" s="29" t="s">
         <v>635</v>
@@ -12515,10 +12515,10 @@
         <v>54</v>
       </c>
       <c r="L179" s="30">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="M179" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="180" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12538,7 +12538,7 @@
         <v>640</v>
       </c>
       <c r="F180" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G180" s="21" t="s">
         <v>641</v>
@@ -12556,10 +12556,10 @@
         <v>54</v>
       </c>
       <c r="L180" s="23">
-        <v>99</v>
+        <v>299</v>
       </c>
       <c r="M180" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="181" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12576,31 +12576,31 @@
         <v>67</v>
       </c>
       <c r="E181" s="28" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F181" s="29" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G181" s="29" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H181" s="29" t="s">
         <v>745</v>
       </c>
       <c r="I181" s="29" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="J181" s="29" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="K181" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L181" s="30">
-        <v>546</v>
+        <v>490</v>
       </c>
       <c r="M181" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="182" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12638,10 +12638,10 @@
         <v>54</v>
       </c>
       <c r="L182" s="23">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="M182" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="183" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12679,10 +12679,10 @@
         <v>54</v>
       </c>
       <c r="L183" s="30">
-        <v>117</v>
+        <v>442</v>
       </c>
       <c r="M183" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="184" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12720,10 +12720,10 @@
         <v>54</v>
       </c>
       <c r="L184" s="23">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="M184" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="185" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12761,10 +12761,10 @@
         <v>54</v>
       </c>
       <c r="L185" s="30">
-        <v>250</v>
+        <v>351</v>
       </c>
       <c r="M185" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12802,10 +12802,10 @@
         <v>54</v>
       </c>
       <c r="L186" s="23">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="M186" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="187" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12843,10 +12843,10 @@
         <v>54</v>
       </c>
       <c r="L187" s="30">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="M187" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="188" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12884,10 +12884,10 @@
         <v>54</v>
       </c>
       <c r="L188" s="23">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="M188" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="189" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12925,10 +12925,10 @@
         <v>54</v>
       </c>
       <c r="L189" s="30">
-        <v>194</v>
+        <v>257</v>
       </c>
       <c r="M189" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="190" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12966,10 +12966,10 @@
         <v>54</v>
       </c>
       <c r="L190" s="23">
-        <v>230</v>
+        <v>106</v>
       </c>
       <c r="M190" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="191" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13007,10 +13007,10 @@
         <v>54</v>
       </c>
       <c r="L191" s="30">
-        <v>194</v>
+        <v>275</v>
       </c>
       <c r="M191" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="192" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13048,10 +13048,10 @@
         <v>54</v>
       </c>
       <c r="L192" s="23">
-        <v>388</v>
+        <v>226</v>
       </c>
       <c r="M192" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="193" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13089,10 +13089,10 @@
         <v>54</v>
       </c>
       <c r="L193" s="30">
-        <v>532</v>
+        <v>115</v>
       </c>
       <c r="M193" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="194" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13130,10 +13130,10 @@
         <v>54</v>
       </c>
       <c r="L194" s="23">
-        <v>89</v>
+        <v>368</v>
       </c>
       <c r="M194" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="195" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13171,10 +13171,10 @@
         <v>54</v>
       </c>
       <c r="L195" s="30">
-        <v>395</v>
+        <v>78</v>
       </c>
       <c r="M195" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="196" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13212,10 +13212,10 @@
         <v>54</v>
       </c>
       <c r="L196" s="23">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="M196" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="197" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13253,10 +13253,10 @@
         <v>54</v>
       </c>
       <c r="L197" s="30">
-        <v>195</v>
+        <v>327</v>
       </c>
       <c r="M197" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="198" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13294,10 +13294,10 @@
         <v>54</v>
       </c>
       <c r="L198" s="23">
-        <v>454</v>
+        <v>317</v>
       </c>
       <c r="M198" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="199" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13335,10 +13335,10 @@
         <v>54</v>
       </c>
       <c r="L199" s="30">
-        <v>251</v>
+        <v>102</v>
       </c>
       <c r="M199" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="200" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13376,10 +13376,10 @@
         <v>54</v>
       </c>
       <c r="L200" s="23">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="M200" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="201" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13417,10 +13417,10 @@
         <v>54</v>
       </c>
       <c r="L201" s="30">
-        <v>345</v>
+        <v>448</v>
       </c>
       <c r="M201" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="202" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13458,10 +13458,10 @@
         <v>54</v>
       </c>
       <c r="L202" s="23">
-        <v>429</v>
+        <v>122</v>
       </c>
       <c r="M202" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="203" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13499,10 +13499,10 @@
         <v>54</v>
       </c>
       <c r="L203" s="30">
-        <v>245</v>
+        <v>204</v>
       </c>
       <c r="M203" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="204" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13540,10 +13540,10 @@
         <v>54</v>
       </c>
       <c r="L204" s="23">
-        <v>466</v>
+        <v>297</v>
       </c>
       <c r="M204" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="205" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13581,10 +13581,10 @@
         <v>54</v>
       </c>
       <c r="L205" s="30">
-        <v>252</v>
+        <v>162</v>
       </c>
       <c r="M205" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="206" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13622,10 +13622,10 @@
         <v>54</v>
       </c>
       <c r="L206" s="23">
-        <v>496</v>
+        <v>550</v>
       </c>
       <c r="M206" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="207" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13663,10 +13663,10 @@
         <v>54</v>
       </c>
       <c r="L207" s="30">
-        <v>88</v>
+        <v>201</v>
       </c>
       <c r="M207" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="208" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13704,10 +13704,10 @@
         <v>54</v>
       </c>
       <c r="L208" s="23">
-        <v>274</v>
+        <v>458</v>
       </c>
       <c r="M208" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="209" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13745,10 +13745,10 @@
         <v>54</v>
       </c>
       <c r="L209" s="30">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="M209" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="210" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13786,10 +13786,10 @@
         <v>54</v>
       </c>
       <c r="L210" s="23">
-        <v>209</v>
+        <v>272</v>
       </c>
       <c r="M210" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="211" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13827,10 +13827,10 @@
         <v>54</v>
       </c>
       <c r="L211" s="30">
-        <v>487</v>
+        <v>168</v>
       </c>
       <c r="M211" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="212" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13868,10 +13868,10 @@
         <v>54</v>
       </c>
       <c r="L212" s="23">
-        <v>260</v>
+        <v>84</v>
       </c>
       <c r="M212" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="213" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13909,10 +13909,10 @@
         <v>54</v>
       </c>
       <c r="L213" s="30">
-        <v>470</v>
+        <v>375</v>
       </c>
       <c r="M213" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="214" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13950,10 +13950,10 @@
         <v>54</v>
       </c>
       <c r="L214" s="23">
-        <v>245</v>
+        <v>140</v>
       </c>
       <c r="M214" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="215" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13991,10 +13991,10 @@
         <v>54</v>
       </c>
       <c r="L215" s="30">
-        <v>285</v>
+        <v>406</v>
       </c>
       <c r="M215" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="216" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14032,10 +14032,10 @@
         <v>54</v>
       </c>
       <c r="L216" s="23">
-        <v>335</v>
+        <v>537</v>
       </c>
       <c r="M216" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="217" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14073,10 +14073,10 @@
         <v>54</v>
       </c>
       <c r="L217" s="30">
-        <v>418</v>
+        <v>307</v>
       </c>
       <c r="M217" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="218" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14114,10 +14114,10 @@
         <v>54</v>
       </c>
       <c r="L218" s="23">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M218" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="219" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14155,10 +14155,10 @@
         <v>54</v>
       </c>
       <c r="L219" s="30">
-        <v>514</v>
+        <v>83</v>
       </c>
       <c r="M219" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="220" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14196,10 +14196,10 @@
         <v>54</v>
       </c>
       <c r="L220" s="23">
-        <v>97</v>
+        <v>549</v>
       </c>
       <c r="M220" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="221" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14237,10 +14237,10 @@
         <v>54</v>
       </c>
       <c r="L221" s="30">
-        <v>401</v>
+        <v>240</v>
       </c>
       <c r="M221" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="222" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14278,10 +14278,10 @@
         <v>54</v>
       </c>
       <c r="L222" s="23">
-        <v>361</v>
+        <v>392</v>
       </c>
       <c r="M222" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="223" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14319,10 +14319,10 @@
         <v>54</v>
       </c>
       <c r="L223" s="30">
-        <v>291</v>
+        <v>185</v>
       </c>
       <c r="M223" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="224" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14360,10 +14360,10 @@
         <v>54</v>
       </c>
       <c r="L224" s="23">
-        <v>172</v>
+        <v>465</v>
       </c>
       <c r="M224" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="225" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14401,10 +14401,10 @@
         <v>54</v>
       </c>
       <c r="L225" s="30">
-        <v>244</v>
+        <v>379</v>
       </c>
       <c r="M225" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="226" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14442,10 +14442,10 @@
         <v>54</v>
       </c>
       <c r="L226" s="23">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="M226" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="227" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14483,10 +14483,10 @@
         <v>54</v>
       </c>
       <c r="L227" s="30">
-        <v>157</v>
+        <v>296</v>
       </c>
       <c r="M227" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="228" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14524,10 +14524,10 @@
         <v>54</v>
       </c>
       <c r="L228" s="23">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="M228" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="229" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14565,10 +14565,10 @@
         <v>54</v>
       </c>
       <c r="L229" s="30">
-        <v>276</v>
+        <v>92</v>
       </c>
       <c r="M229" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="230" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14606,10 +14606,10 @@
         <v>54</v>
       </c>
       <c r="L230" s="23">
-        <v>85</v>
+        <v>247</v>
       </c>
       <c r="M230" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="231" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14647,10 +14647,10 @@
         <v>54</v>
       </c>
       <c r="L231" s="30">
-        <v>497</v>
+        <v>248</v>
       </c>
       <c r="M231" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="232" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14688,10 +14688,10 @@
         <v>54</v>
       </c>
       <c r="L232" s="23">
-        <v>85</v>
+        <v>304</v>
       </c>
       <c r="M232" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="233" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14729,10 +14729,10 @@
         <v>54</v>
       </c>
       <c r="L233" s="30">
-        <v>335</v>
+        <v>265</v>
       </c>
       <c r="M233" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="234" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14770,10 +14770,10 @@
         <v>54</v>
       </c>
       <c r="L234" s="23">
-        <v>406</v>
+        <v>528</v>
       </c>
       <c r="M234" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="235" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14811,10 +14811,10 @@
         <v>54</v>
       </c>
       <c r="L235" s="30">
-        <v>374</v>
+        <v>457</v>
       </c>
       <c r="M235" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="236" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14852,10 +14852,10 @@
         <v>54</v>
       </c>
       <c r="L236" s="23">
-        <v>149</v>
+        <v>431</v>
       </c>
       <c r="M236" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="237" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14893,10 +14893,10 @@
         <v>54</v>
       </c>
       <c r="L237" s="30">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="M237" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="238" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14934,10 +14934,10 @@
         <v>54</v>
       </c>
       <c r="L238" s="23">
-        <v>547</v>
+        <v>508</v>
       </c>
       <c r="M238" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="239" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -14975,10 +14975,10 @@
         <v>54</v>
       </c>
       <c r="L239" s="30">
-        <v>225</v>
+        <v>376</v>
       </c>
       <c r="M239" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="240" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -15016,10 +15016,10 @@
         <v>54</v>
       </c>
       <c r="L240" s="23">
-        <v>390</v>
+        <v>438</v>
       </c>
       <c r="M240" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="241" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -15057,10 +15057,10 @@
         <v>54</v>
       </c>
       <c r="L241" s="30">
-        <v>471</v>
+        <v>237</v>
       </c>
       <c r="M241" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="242" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -15098,10 +15098,10 @@
         <v>54</v>
       </c>
       <c r="L242" s="23">
-        <v>243</v>
+        <v>539</v>
       </c>
       <c r="M242" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="243" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -15139,10 +15139,10 @@
         <v>54</v>
       </c>
       <c r="L243" s="30">
-        <v>541</v>
+        <v>211</v>
       </c>
       <c r="M243" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="244" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -15180,10 +15180,10 @@
         <v>54</v>
       </c>
       <c r="L244" s="23">
-        <v>500</v>
+        <v>387</v>
       </c>
       <c r="M244" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="245" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -15221,10 +15221,10 @@
         <v>54</v>
       </c>
       <c r="L245" s="30">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="M245" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="246" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -15262,10 +15262,10 @@
         <v>54</v>
       </c>
       <c r="L246" s="23">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="M246" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="247" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -15303,10 +15303,10 @@
         <v>54</v>
       </c>
       <c r="L247" s="30">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="M247" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="248" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -15344,10 +15344,10 @@
         <v>54</v>
       </c>
       <c r="L248" s="23">
-        <v>207</v>
+        <v>346</v>
       </c>
       <c r="M248" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="249" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -15385,10 +15385,10 @@
         <v>54</v>
       </c>
       <c r="L249" s="30">
-        <v>300</v>
+        <v>165</v>
       </c>
       <c r="M249" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="250" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -15426,10 +15426,10 @@
         <v>54</v>
       </c>
       <c r="L250" s="23">
-        <v>200</v>
+        <v>472</v>
       </c>
       <c r="M250" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="251" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -15467,10 +15467,10 @@
         <v>54</v>
       </c>
       <c r="L251" s="30">
-        <v>452</v>
+        <v>394</v>
       </c>
       <c r="M251" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="252" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -15508,10 +15508,10 @@
         <v>54</v>
       </c>
       <c r="L252" s="23">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="M252" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="253" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -15549,10 +15549,10 @@
         <v>54</v>
       </c>
       <c r="L253" s="30">
-        <v>501</v>
+        <v>297</v>
       </c>
       <c r="M253" s="31" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="254" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -15590,10 +15590,10 @@
         <v>54</v>
       </c>
       <c r="L254" s="23">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="M254" s="24" t="s">
-        <v>589</v>
+        <v>386</v>
       </c>
     </row>
     <row r="255" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -15631,21 +15631,21 @@
         <v>54</v>
       </c>
       <c r="L255" s="30">
-        <v>202</v>
+        <v>401</v>
       </c>
       <c r="M255" s="31" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="256" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A256" s="16" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B256" s="17" t="s">
         <v>27</v>
       </c>
       <c r="C256" s="18" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D256" s="32" t="s">
         <v>62</v>
@@ -15660,7 +15660,7 @@
         <v>952</v>
       </c>
       <c r="H256" s="21" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="I256" s="21" t="s">
         <v>954</v>
@@ -15672,21 +15672,21 @@
         <v>54</v>
       </c>
       <c r="L256" s="23">
-        <v>145</v>
+        <v>386</v>
       </c>
       <c r="M256" s="24" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="257" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A257" s="25" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B257" s="26" t="s">
         <v>27</v>
       </c>
       <c r="C257" s="27" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D257" s="19" t="s">
         <v>47</v>
@@ -15701,7 +15701,7 @@
         <v>958</v>
       </c>
       <c r="H257" s="29" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="I257" s="29" t="s">
         <v>960</v>
@@ -15713,21 +15713,21 @@
         <v>54</v>
       </c>
       <c r="L257" s="30">
-        <v>292</v>
+        <v>533</v>
       </c>
       <c r="M257" s="31" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="258" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A258" s="16" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B258" s="17" t="s">
         <v>27</v>
       </c>
       <c r="C258" s="18" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D258" s="19" t="s">
         <v>47</v>
@@ -15742,7 +15742,7 @@
         <v>892</v>
       </c>
       <c r="H258" s="21" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="I258" s="21" t="s">
         <v>894</v>
@@ -15754,21 +15754,21 @@
         <v>54</v>
       </c>
       <c r="L258" s="23">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="M258" s="24" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="259" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A259" s="25" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B259" s="26" t="s">
         <v>27</v>
       </c>
       <c r="C259" s="27" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D259" s="32" t="s">
         <v>67</v>
@@ -15783,7 +15783,7 @@
         <v>898</v>
       </c>
       <c r="H259" s="29" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="I259" s="29" t="s">
         <v>900</v>
@@ -15795,21 +15795,21 @@
         <v>54</v>
       </c>
       <c r="L259" s="30">
-        <v>186</v>
+        <v>342</v>
       </c>
       <c r="M259" s="31" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="260" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A260" s="16" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B260" s="17" t="s">
         <v>27</v>
       </c>
       <c r="C260" s="18" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="D260" s="32" t="s">
         <v>62</v>
@@ -15824,7 +15824,7 @@
         <v>904</v>
       </c>
       <c r="H260" s="21" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="I260" s="21" t="s">
         <v>906</v>
@@ -15836,21 +15836,21 @@
         <v>54</v>
       </c>
       <c r="L260" s="23">
-        <v>100</v>
+        <v>349</v>
       </c>
       <c r="M260" s="24" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="261" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A261" s="25" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B261" s="26" t="s">
         <v>27</v>
       </c>
       <c r="C261" s="27" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="D261" s="32" t="s">
         <v>62</v>
@@ -15865,7 +15865,7 @@
         <v>910</v>
       </c>
       <c r="H261" s="29" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="I261" s="29" t="s">
         <v>912</v>
@@ -15877,21 +15877,21 @@
         <v>54</v>
       </c>
       <c r="L261" s="30">
-        <v>421</v>
+        <v>497</v>
       </c>
       <c r="M261" s="31" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="262" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A262" s="16" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B262" s="17" t="s">
         <v>27</v>
       </c>
       <c r="C262" s="18" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="D262" s="32" t="s">
         <v>62</v>
@@ -15906,7 +15906,7 @@
         <v>916</v>
       </c>
       <c r="H262" s="21" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="I262" s="21" t="s">
         <v>918</v>
@@ -15918,21 +15918,21 @@
         <v>54</v>
       </c>
       <c r="L262" s="23">
-        <v>325</v>
+        <v>115</v>
       </c>
       <c r="M262" s="24" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="263" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A263" s="25" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B263" s="26" t="s">
         <v>27</v>
       </c>
       <c r="C263" s="27" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="D263" s="32" t="s">
         <v>67</v>
@@ -15947,7 +15947,7 @@
         <v>922</v>
       </c>
       <c r="H263" s="29" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="I263" s="29" t="s">
         <v>924</v>
@@ -15959,21 +15959,21 @@
         <v>54</v>
       </c>
       <c r="L263" s="30">
-        <v>194</v>
+        <v>325</v>
       </c>
       <c r="M263" s="31" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="264" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A264" s="16" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B264" s="17" t="s">
         <v>27</v>
       </c>
       <c r="C264" s="18" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D264" s="32" t="s">
         <v>67</v>
@@ -15988,7 +15988,7 @@
         <v>928</v>
       </c>
       <c r="H264" s="21" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="I264" s="21" t="s">
         <v>930</v>
@@ -16000,21 +16000,21 @@
         <v>54</v>
       </c>
       <c r="L264" s="23">
-        <v>508</v>
+        <v>424</v>
       </c>
       <c r="M264" s="24" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="265" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A265" s="25" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B265" s="26" t="s">
         <v>27</v>
       </c>
       <c r="C265" s="27" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="D265" s="32" t="s">
         <v>67</v>
@@ -16029,7 +16029,7 @@
         <v>934</v>
       </c>
       <c r="H265" s="29" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="I265" s="29" t="s">
         <v>936</v>
@@ -16041,21 +16041,21 @@
         <v>54</v>
       </c>
       <c r="L265" s="30">
-        <v>485</v>
+        <v>291</v>
       </c>
       <c r="M265" s="31" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="266" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A266" s="16" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B266" s="17" t="s">
         <v>27</v>
       </c>
       <c r="C266" s="18" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="D266" s="19" t="s">
         <v>47</v>
@@ -16070,7 +16070,7 @@
         <v>940</v>
       </c>
       <c r="H266" s="21" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="I266" s="21" t="s">
         <v>942</v>
@@ -16082,1322 +16082,1322 @@
         <v>54</v>
       </c>
       <c r="L266" s="23">
-        <v>308</v>
+        <v>158</v>
       </c>
       <c r="M266" s="24" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="267" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A267" s="25" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B267" s="26" t="s">
         <v>29</v>
       </c>
       <c r="C267" s="27" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="D267" s="19" t="s">
         <v>47</v>
       </c>
       <c r="E267" s="28" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="F267" s="29" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G267" s="29" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H267" s="29" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="I267" s="29" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="J267" s="29" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="K267" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L267" s="30">
-        <v>146</v>
+        <v>214</v>
       </c>
       <c r="M267" s="31" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="268" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A268" s="16" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B268" s="17" t="s">
         <v>29</v>
       </c>
       <c r="C268" s="18" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="D268" s="19" t="s">
         <v>47</v>
       </c>
       <c r="E268" s="20" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="F268" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G268" s="21" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H268" s="21" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="I268" s="21" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="J268" s="21" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="K268" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L268" s="23">
-        <v>85</v>
+        <v>459</v>
       </c>
       <c r="M268" s="24" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="269" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A269" s="25" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B269" s="26" t="s">
         <v>29</v>
       </c>
       <c r="C269" s="27" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="D269" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E269" s="28" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="F269" s="29" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G269" s="29" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H269" s="29" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="I269" s="29" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="J269" s="29" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="K269" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L269" s="30">
-        <v>308</v>
+        <v>93</v>
       </c>
       <c r="M269" s="31" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="270" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A270" s="16" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B270" s="17" t="s">
         <v>29</v>
       </c>
       <c r="C270" s="18" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="D270" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E270" s="20" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F270" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G270" s="21" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H270" s="21" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I270" s="21" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J270" s="21" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="K270" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L270" s="23">
-        <v>285</v>
+        <v>528</v>
       </c>
       <c r="M270" s="24" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="271" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A271" s="25" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B271" s="26" t="s">
         <v>29</v>
       </c>
       <c r="C271" s="27" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="D271" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E271" s="28" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="F271" s="29" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G271" s="29" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H271" s="29" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="I271" s="29" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="J271" s="29" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="K271" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L271" s="30">
-        <v>367</v>
+        <v>342</v>
       </c>
       <c r="M271" s="31" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="272" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A272" s="16" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B272" s="17" t="s">
         <v>29</v>
       </c>
       <c r="C272" s="18" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="D272" s="19" t="s">
         <v>47</v>
       </c>
       <c r="E272" s="20" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="F272" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G272" s="21" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H272" s="21" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="I272" s="21" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="J272" s="21" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="K272" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L272" s="23">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="M272" s="24" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="273" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A273" s="25" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B273" s="26" t="s">
         <v>29</v>
       </c>
       <c r="C273" s="27" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="D273" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E273" s="28" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="F273" s="29" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G273" s="29" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H273" s="29" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="I273" s="29" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="J273" s="29" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="K273" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L273" s="30">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="M273" s="31" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="274" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A274" s="16" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B274" s="17" t="s">
         <v>29</v>
       </c>
       <c r="C274" s="18" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="D274" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E274" s="20" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="F274" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G274" s="21" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H274" s="21" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="I274" s="21" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="J274" s="21" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="K274" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L274" s="23">
-        <v>447</v>
+        <v>323</v>
       </c>
       <c r="M274" s="24" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="275" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A275" s="25" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B275" s="26" t="s">
         <v>29</v>
       </c>
       <c r="C275" s="27" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D275" s="32" t="s">
         <v>67</v>
       </c>
       <c r="E275" s="28" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="F275" s="29" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G275" s="29" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H275" s="29" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="I275" s="29" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="J275" s="29" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="K275" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L275" s="30">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="M275" s="31" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="276" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A276" s="16" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B276" s="17" t="s">
         <v>29</v>
       </c>
       <c r="C276" s="18" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D276" s="19" t="s">
         <v>47</v>
       </c>
       <c r="E276" s="20" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F276" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G276" s="21" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H276" s="21" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="I276" s="21" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="J276" s="21" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="K276" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L276" s="23">
-        <v>91</v>
+        <v>181</v>
       </c>
       <c r="M276" s="24" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="277" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A277" s="25" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B277" s="26" t="s">
         <v>29</v>
       </c>
       <c r="C277" s="27" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D277" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E277" s="28" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="F277" s="29" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G277" s="29" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H277" s="29" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="I277" s="29" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="J277" s="29" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="K277" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L277" s="30">
-        <v>438</v>
+        <v>301</v>
       </c>
       <c r="M277" s="31" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="278" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A278" s="16" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B278" s="17" t="s">
         <v>29</v>
       </c>
       <c r="C278" s="18" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="D278" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E278" s="20" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="F278" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G278" s="21" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H278" s="21" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="I278" s="21" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="J278" s="21" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="K278" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L278" s="23">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="M278" s="24" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="279" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A279" s="25" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B279" s="26" t="s">
         <v>29</v>
       </c>
       <c r="C279" s="27" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="D279" s="19" t="s">
         <v>47</v>
       </c>
       <c r="E279" s="28" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="F279" s="29" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G279" s="29" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H279" s="29" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="I279" s="29" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="J279" s="29" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="K279" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L279" s="30">
-        <v>363</v>
+        <v>183</v>
       </c>
       <c r="M279" s="31" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="280" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A280" s="16" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B280" s="17" t="s">
         <v>29</v>
       </c>
       <c r="C280" s="18" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="D280" s="19" t="s">
         <v>47</v>
       </c>
       <c r="E280" s="20" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="F280" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G280" s="21" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H280" s="21" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="I280" s="21" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="J280" s="21" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="K280" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L280" s="23">
-        <v>97</v>
+        <v>537</v>
       </c>
       <c r="M280" s="24" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="281" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A281" s="25" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B281" s="26" t="s">
         <v>29</v>
       </c>
       <c r="C281" s="27" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="D281" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E281" s="28" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="F281" s="29" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G281" s="29" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H281" s="29" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="I281" s="29" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="J281" s="29" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="K281" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L281" s="30">
-        <v>370</v>
+        <v>460</v>
       </c>
       <c r="M281" s="31" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="282" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A282" s="16" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B282" s="17" t="s">
         <v>29</v>
       </c>
       <c r="C282" s="18" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="D282" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E282" s="20" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F282" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G282" s="21" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H282" s="21" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="I282" s="21" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J282" s="21" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="K282" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L282" s="23">
-        <v>533</v>
+        <v>102</v>
       </c>
       <c r="M282" s="24" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="283" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A283" s="25" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B283" s="26" t="s">
         <v>29</v>
       </c>
       <c r="C283" s="27" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="D283" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E283" s="28" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="F283" s="29" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G283" s="29" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H283" s="29" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="I283" s="29" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="J283" s="29" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="K283" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L283" s="30">
-        <v>470</v>
+        <v>257</v>
       </c>
       <c r="M283" s="31" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="284" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A284" s="16" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B284" s="17" t="s">
         <v>29</v>
       </c>
       <c r="C284" s="18" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="D284" s="19" t="s">
         <v>47</v>
       </c>
       <c r="E284" s="20" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="F284" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G284" s="21" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H284" s="21" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="I284" s="21" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="J284" s="21" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="K284" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L284" s="23">
-        <v>266</v>
+        <v>361</v>
       </c>
       <c r="M284" s="24" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="285" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A285" s="25" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B285" s="26" t="s">
         <v>29</v>
       </c>
       <c r="C285" s="27" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="D285" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E285" s="28" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="F285" s="29" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G285" s="29" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H285" s="29" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="I285" s="29" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="J285" s="29" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="K285" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L285" s="30">
-        <v>335</v>
+        <v>450</v>
       </c>
       <c r="M285" s="31" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="286" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A286" s="16" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B286" s="17" t="s">
         <v>29</v>
       </c>
       <c r="C286" s="18" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="D286" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E286" s="20" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="F286" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G286" s="21" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H286" s="21" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="I286" s="21" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="J286" s="21" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="K286" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L286" s="23">
-        <v>150</v>
+        <v>256</v>
       </c>
       <c r="M286" s="24" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="287" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A287" s="25" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B287" s="26" t="s">
         <v>29</v>
       </c>
       <c r="C287" s="27" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="D287" s="32" t="s">
         <v>67</v>
       </c>
       <c r="E287" s="28" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="F287" s="29" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G287" s="29" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H287" s="29" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="I287" s="29" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="J287" s="29" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="K287" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L287" s="30">
-        <v>162</v>
+        <v>246</v>
       </c>
       <c r="M287" s="31" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="288" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A288" s="16" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B288" s="17" t="s">
         <v>29</v>
       </c>
       <c r="C288" s="18" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="D288" s="19" t="s">
         <v>47</v>
       </c>
       <c r="E288" s="20" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F288" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G288" s="21" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H288" s="21" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="I288" s="21" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="J288" s="21" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="K288" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L288" s="23">
-        <v>480</v>
+        <v>217</v>
       </c>
       <c r="M288" s="24" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="289" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A289" s="25" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B289" s="26" t="s">
         <v>29</v>
       </c>
       <c r="C289" s="27" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="D289" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E289" s="28" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="F289" s="29" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G289" s="29" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H289" s="29" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="I289" s="29" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="J289" s="29" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="K289" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L289" s="30">
-        <v>426</v>
+        <v>108</v>
       </c>
       <c r="M289" s="31" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="290" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A290" s="16" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B290" s="17" t="s">
         <v>29</v>
       </c>
       <c r="C290" s="18" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="D290" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E290" s="20" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="F290" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G290" s="21" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H290" s="21" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="I290" s="21" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="J290" s="21" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="K290" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L290" s="23">
-        <v>218</v>
+        <v>461</v>
       </c>
       <c r="M290" s="24" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="291" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A291" s="25" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B291" s="26" t="s">
         <v>29</v>
       </c>
       <c r="C291" s="27" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="D291" s="19" t="s">
         <v>47</v>
       </c>
       <c r="E291" s="28" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="F291" s="29" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G291" s="29" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H291" s="29" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="I291" s="29" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="J291" s="29" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="K291" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L291" s="30">
-        <v>246</v>
+        <v>295</v>
       </c>
       <c r="M291" s="31" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="292" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A292" s="16" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B292" s="17" t="s">
         <v>29</v>
       </c>
       <c r="C292" s="18" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="D292" s="19" t="s">
         <v>47</v>
       </c>
       <c r="E292" s="20" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="F292" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G292" s="21" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H292" s="21" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="I292" s="21" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="J292" s="21" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="K292" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L292" s="23">
-        <v>414</v>
+        <v>85</v>
       </c>
       <c r="M292" s="24" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="293" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A293" s="25" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B293" s="26" t="s">
         <v>29</v>
       </c>
       <c r="C293" s="27" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="D293" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E293" s="28" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="F293" s="29" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G293" s="29" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H293" s="29" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="I293" s="29" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="J293" s="29" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="K293" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L293" s="30">
-        <v>510</v>
+        <v>212</v>
       </c>
       <c r="M293" s="31" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="294" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A294" s="16" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B294" s="17" t="s">
         <v>29</v>
       </c>
       <c r="C294" s="18" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="D294" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E294" s="20" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F294" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G294" s="21" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H294" s="21" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="I294" s="21" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J294" s="21" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="K294" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L294" s="23">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="M294" s="24" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="295" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A295" s="25" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B295" s="26" t="s">
         <v>29</v>
       </c>
       <c r="C295" s="27" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="D295" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E295" s="28" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="F295" s="29" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G295" s="29" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H295" s="29" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="I295" s="29" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="J295" s="29" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="K295" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L295" s="30">
-        <v>519</v>
+        <v>212</v>
       </c>
       <c r="M295" s="31" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="296" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A296" s="16" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B296" s="17" t="s">
         <v>29</v>
       </c>
       <c r="C296" s="18" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="D296" s="19" t="s">
         <v>47</v>
       </c>
       <c r="E296" s="20" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="F296" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G296" s="21" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H296" s="21" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="I296" s="21" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="J296" s="21" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="K296" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L296" s="23">
-        <v>188</v>
+        <v>336</v>
       </c>
       <c r="M296" s="24" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="297" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A297" s="25" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B297" s="26" t="s">
         <v>29</v>
       </c>
       <c r="C297" s="27" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="D297" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E297" s="28" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="F297" s="29" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G297" s="29" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H297" s="29" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="I297" s="29" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="J297" s="29" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="K297" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L297" s="30">
-        <v>113</v>
+        <v>185</v>
       </c>
       <c r="M297" s="31" t="s">
-        <v>589</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="298" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A298" s="16" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B298" s="17" t="s">
         <v>29</v>
       </c>
       <c r="C298" s="18" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="D298" s="32" t="s">
         <v>62</v>
       </c>
       <c r="E298" s="20" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="F298" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G298" s="21" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H298" s="21" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="I298" s="21" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="J298" s="21" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="K298" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L298" s="23">
-        <v>478</v>
+        <v>375</v>
       </c>
       <c r="M298" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="299" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -17414,31 +17414,31 @@
         <v>67</v>
       </c>
       <c r="E299" s="28" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="F299" s="29" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G299" s="29" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H299" s="29" t="s">
         <v>1196</v>
       </c>
       <c r="I299" s="29" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="J299" s="29" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="K299" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L299" s="30">
-        <v>170</v>
+        <v>131</v>
       </c>
       <c r="M299" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="300" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -17455,31 +17455,31 @@
         <v>47</v>
       </c>
       <c r="E300" s="20" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F300" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G300" s="21" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H300" s="21" t="s">
         <v>1199</v>
       </c>
       <c r="I300" s="21" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="J300" s="21" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="K300" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L300" s="23">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M300" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="301" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -17496,31 +17496,31 @@
         <v>62</v>
       </c>
       <c r="E301" s="28" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="F301" s="29" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G301" s="29" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H301" s="29" t="s">
         <v>1202</v>
       </c>
       <c r="I301" s="29" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="J301" s="29" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="K301" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L301" s="30">
-        <v>425</v>
+        <v>363</v>
       </c>
       <c r="M301" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="302" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -17537,31 +17537,31 @@
         <v>62</v>
       </c>
       <c r="E302" s="20" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="F302" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G302" s="21" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H302" s="21" t="s">
         <v>1205</v>
       </c>
       <c r="I302" s="21" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="J302" s="21" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="K302" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L302" s="23">
-        <v>224</v>
+        <v>111</v>
       </c>
       <c r="M302" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="303" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -17578,31 +17578,31 @@
         <v>47</v>
       </c>
       <c r="E303" s="28" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="F303" s="29" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G303" s="29" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H303" s="29" t="s">
         <v>1208</v>
       </c>
       <c r="I303" s="29" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="J303" s="29" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="K303" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L303" s="30">
-        <v>138</v>
+        <v>246</v>
       </c>
       <c r="M303" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="304" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -17619,31 +17619,31 @@
         <v>47</v>
       </c>
       <c r="E304" s="20" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="F304" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G304" s="21" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H304" s="21" t="s">
         <v>1211</v>
       </c>
       <c r="I304" s="21" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="J304" s="21" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="K304" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L304" s="23">
-        <v>224</v>
+        <v>114</v>
       </c>
       <c r="M304" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="305" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -17660,31 +17660,31 @@
         <v>62</v>
       </c>
       <c r="E305" s="28" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="F305" s="29" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G305" s="29" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H305" s="29" t="s">
         <v>1214</v>
       </c>
       <c r="I305" s="29" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="J305" s="29" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="K305" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L305" s="30">
-        <v>78</v>
+        <v>272</v>
       </c>
       <c r="M305" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="306" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -17701,31 +17701,31 @@
         <v>62</v>
       </c>
       <c r="E306" s="20" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F306" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G306" s="21" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H306" s="21" t="s">
         <v>1217</v>
       </c>
       <c r="I306" s="21" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J306" s="21" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="K306" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L306" s="23">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="M306" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="307" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -17742,31 +17742,31 @@
         <v>62</v>
       </c>
       <c r="E307" s="28" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="F307" s="29" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G307" s="29" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H307" s="29" t="s">
         <v>1220</v>
       </c>
       <c r="I307" s="29" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="J307" s="29" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="K307" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L307" s="30">
-        <v>286</v>
+        <v>454</v>
       </c>
       <c r="M307" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="308" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -17783,31 +17783,31 @@
         <v>47</v>
       </c>
       <c r="E308" s="20" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="F308" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G308" s="21" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H308" s="21" t="s">
         <v>1223</v>
       </c>
       <c r="I308" s="21" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="J308" s="21" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="K308" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L308" s="23">
-        <v>484</v>
+        <v>403</v>
       </c>
       <c r="M308" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="309" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -17824,31 +17824,31 @@
         <v>62</v>
       </c>
       <c r="E309" s="28" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="F309" s="29" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G309" s="29" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H309" s="29" t="s">
         <v>1226</v>
       </c>
       <c r="I309" s="29" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="J309" s="29" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="K309" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L309" s="30">
-        <v>455</v>
+        <v>405</v>
       </c>
       <c r="M309" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="310" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -17865,31 +17865,31 @@
         <v>62</v>
       </c>
       <c r="E310" s="20" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="F310" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G310" s="21" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H310" s="21" t="s">
         <v>1229</v>
       </c>
       <c r="I310" s="21" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="J310" s="21" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="K310" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L310" s="23">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M310" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="311" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -17906,31 +17906,31 @@
         <v>67</v>
       </c>
       <c r="E311" s="28" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="F311" s="29" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G311" s="29" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H311" s="29" t="s">
         <v>1232</v>
       </c>
       <c r="I311" s="29" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="J311" s="29" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="K311" s="22" t="s">
         <v>54</v>
       </c>
       <c r="L311" s="30">
-        <v>434</v>
+        <v>543</v>
       </c>
       <c r="M311" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="312" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -17968,10 +17968,10 @@
         <v>54</v>
       </c>
       <c r="L312" s="23">
-        <v>372</v>
+        <v>484</v>
       </c>
       <c r="M312" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="313" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18009,10 +18009,10 @@
         <v>54</v>
       </c>
       <c r="L313" s="30">
-        <v>431</v>
+        <v>201</v>
       </c>
       <c r="M313" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="314" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18050,10 +18050,10 @@
         <v>54</v>
       </c>
       <c r="L314" s="23">
-        <v>481</v>
+        <v>268</v>
       </c>
       <c r="M314" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="315" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18091,10 +18091,10 @@
         <v>54</v>
       </c>
       <c r="L315" s="30">
-        <v>413</v>
+        <v>207</v>
       </c>
       <c r="M315" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="316" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18132,10 +18132,10 @@
         <v>54</v>
       </c>
       <c r="L316" s="23">
-        <v>157</v>
+        <v>379</v>
       </c>
       <c r="M316" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="317" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18173,10 +18173,10 @@
         <v>54</v>
       </c>
       <c r="L317" s="30">
-        <v>418</v>
+        <v>331</v>
       </c>
       <c r="M317" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="318" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18214,10 +18214,10 @@
         <v>54</v>
       </c>
       <c r="L318" s="23">
-        <v>285</v>
+        <v>546</v>
       </c>
       <c r="M318" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="319" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18255,10 +18255,10 @@
         <v>54</v>
       </c>
       <c r="L319" s="30">
-        <v>185</v>
+        <v>453</v>
       </c>
       <c r="M319" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="320" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18296,10 +18296,10 @@
         <v>54</v>
       </c>
       <c r="L320" s="23">
-        <v>228</v>
+        <v>381</v>
       </c>
       <c r="M320" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="321" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18337,10 +18337,10 @@
         <v>54</v>
       </c>
       <c r="L321" s="30">
-        <v>388</v>
+        <v>90</v>
       </c>
       <c r="M321" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="322" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18378,10 +18378,10 @@
         <v>54</v>
       </c>
       <c r="L322" s="23">
-        <v>77</v>
+        <v>441</v>
       </c>
       <c r="M322" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="323" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18419,10 +18419,10 @@
         <v>54</v>
       </c>
       <c r="L323" s="30">
-        <v>459</v>
+        <v>264</v>
       </c>
       <c r="M323" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="324" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18460,10 +18460,10 @@
         <v>54</v>
       </c>
       <c r="L324" s="23">
-        <v>196</v>
+        <v>101</v>
       </c>
       <c r="M324" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="325" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18501,10 +18501,10 @@
         <v>54</v>
       </c>
       <c r="L325" s="30">
-        <v>484</v>
+        <v>369</v>
       </c>
       <c r="M325" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="326" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18542,10 +18542,10 @@
         <v>54</v>
       </c>
       <c r="L326" s="23">
-        <v>333</v>
+        <v>195</v>
       </c>
       <c r="M326" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="327" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18583,10 +18583,10 @@
         <v>54</v>
       </c>
       <c r="L327" s="30">
-        <v>224</v>
+        <v>457</v>
       </c>
       <c r="M327" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="328" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18624,10 +18624,10 @@
         <v>54</v>
       </c>
       <c r="L328" s="23">
-        <v>547</v>
+        <v>155</v>
       </c>
       <c r="M328" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="329" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18665,10 +18665,10 @@
         <v>54</v>
       </c>
       <c r="L329" s="30">
-        <v>253</v>
+        <v>355</v>
       </c>
       <c r="M329" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="330" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18706,10 +18706,10 @@
         <v>54</v>
       </c>
       <c r="L330" s="23">
-        <v>223</v>
+        <v>296</v>
       </c>
       <c r="M330" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="331" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18747,10 +18747,10 @@
         <v>54</v>
       </c>
       <c r="L331" s="30">
-        <v>349</v>
+        <v>373</v>
       </c>
       <c r="M331" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="332" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18788,10 +18788,10 @@
         <v>54</v>
       </c>
       <c r="L332" s="23">
-        <v>440</v>
+        <v>156</v>
       </c>
       <c r="M332" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="333" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18829,10 +18829,10 @@
         <v>54</v>
       </c>
       <c r="L333" s="30">
-        <v>415</v>
+        <v>180</v>
       </c>
       <c r="M333" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="334" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18870,10 +18870,10 @@
         <v>54</v>
       </c>
       <c r="L334" s="23">
-        <v>446</v>
+        <v>106</v>
       </c>
       <c r="M334" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="335" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18911,10 +18911,10 @@
         <v>54</v>
       </c>
       <c r="L335" s="30">
-        <v>228</v>
+        <v>414</v>
       </c>
       <c r="M335" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="336" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18952,10 +18952,10 @@
         <v>54</v>
       </c>
       <c r="L336" s="23">
-        <v>234</v>
+        <v>406</v>
       </c>
       <c r="M336" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="337" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18993,10 +18993,10 @@
         <v>54</v>
       </c>
       <c r="L337" s="30">
-        <v>130</v>
+        <v>455</v>
       </c>
       <c r="M337" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="338" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -19034,10 +19034,10 @@
         <v>54</v>
       </c>
       <c r="L338" s="23">
-        <v>447</v>
+        <v>255</v>
       </c>
       <c r="M338" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="339" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -19075,10 +19075,10 @@
         <v>54</v>
       </c>
       <c r="L339" s="30">
-        <v>497</v>
+        <v>365</v>
       </c>
       <c r="M339" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="340" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -19116,10 +19116,10 @@
         <v>54</v>
       </c>
       <c r="L340" s="23">
-        <v>476</v>
+        <v>263</v>
       </c>
       <c r="M340" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="341" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -19157,10 +19157,10 @@
         <v>54</v>
       </c>
       <c r="L341" s="30">
-        <v>425</v>
+        <v>141</v>
       </c>
       <c r="M341" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="342" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -19198,10 +19198,10 @@
         <v>54</v>
       </c>
       <c r="L342" s="23">
-        <v>107</v>
+        <v>281</v>
       </c>
       <c r="M342" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="343" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -19239,10 +19239,10 @@
         <v>54</v>
       </c>
       <c r="L343" s="30">
-        <v>328</v>
+        <v>149</v>
       </c>
       <c r="M343" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="344" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -19280,10 +19280,10 @@
         <v>54</v>
       </c>
       <c r="L344" s="23">
-        <v>217</v>
+        <v>90</v>
       </c>
       <c r="M344" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="345" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -19321,10 +19321,10 @@
         <v>54</v>
       </c>
       <c r="L345" s="30">
-        <v>158</v>
+        <v>256</v>
       </c>
       <c r="M345" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="346" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -19362,10 +19362,10 @@
         <v>54</v>
       </c>
       <c r="L346" s="23">
-        <v>542</v>
+        <v>133</v>
       </c>
       <c r="M346" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="347" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -19403,10 +19403,10 @@
         <v>54</v>
       </c>
       <c r="L347" s="30">
-        <v>349</v>
+        <v>493</v>
       </c>
       <c r="M347" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="348" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -19444,10 +19444,10 @@
         <v>54</v>
       </c>
       <c r="L348" s="23">
-        <v>403</v>
+        <v>113</v>
       </c>
       <c r="M348" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="349" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -19485,10 +19485,10 @@
         <v>54</v>
       </c>
       <c r="L349" s="30">
-        <v>367</v>
+        <v>156</v>
       </c>
       <c r="M349" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="350" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -19526,10 +19526,10 @@
         <v>54</v>
       </c>
       <c r="L350" s="23">
-        <v>134</v>
+        <v>379</v>
       </c>
       <c r="M350" s="24" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="351" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -19567,10 +19567,10 @@
         <v>54</v>
       </c>
       <c r="L351" s="30">
-        <v>241</v>
+        <v>118</v>
       </c>
       <c r="M351" s="31" t="s">
-        <v>1193</v>
+        <v>1027</v>
       </c>
     </row>
   </sheetData>
